--- a/PORTFOLIO NEW STRUCTURE/template/Portfolio_Tracker_v2.xlsx
+++ b/PORTFOLIO NEW STRUCTURE/template/Portfolio_Tracker_v2.xlsx
@@ -22,10 +22,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -101,22 +103,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" textRotation="45"/>
     </xf>
@@ -124,6 +148,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -358,12 +385,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$B$2:$B$108</f>
+              <f>'Trends'!$B$2:$B$115</f>
             </numRef>
           </val>
         </ser>
@@ -390,12 +417,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$C$2:$C$108</f>
+              <f>'Trends'!$C$2:$C$115</f>
             </numRef>
           </val>
         </ser>
@@ -535,12 +562,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$B$2:$B$108</f>
+              <f>'Trends'!$B$2:$B$115</f>
             </numRef>
           </val>
         </ser>
@@ -567,12 +594,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$C$2:$C$108</f>
+              <f>'Trends'!$C$2:$C$115</f>
             </numRef>
           </val>
         </ser>
@@ -685,12 +712,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$D$2:$D$108</f>
+              <f>'Trends'!$D$2:$D$115</f>
             </numRef>
           </val>
         </ser>
@@ -717,12 +744,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$E$2:$E$108</f>
+              <f>'Trends'!$E$2:$E$115</f>
             </numRef>
           </val>
         </ser>
@@ -805,12 +832,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$F$2:$F$108</f>
+              <f>'Trends'!$F$2:$F$115</f>
             </numRef>
           </val>
         </ser>
@@ -837,12 +864,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$G$2:$G$108</f>
+              <f>'Trends'!$G$2:$G$115</f>
             </numRef>
           </val>
         </ser>
@@ -869,12 +896,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$H$2:$H$108</f>
+              <f>'Trends'!$H$2:$H$115</f>
             </numRef>
           </val>
         </ser>
@@ -901,12 +928,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$I$2:$I$108</f>
+              <f>'Trends'!$I$2:$I$115</f>
             </numRef>
           </val>
         </ser>
@@ -933,12 +960,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Trends'!$A$2:$A$108</f>
+              <f>'Trends'!$A$2:$A$115</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Trends'!$J$2:$J$108</f>
+              <f>'Trends'!$J$2:$J$115</f>
             </numRef>
           </val>
         </ser>
@@ -1178,7 +1205,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="2880000"/>
@@ -1200,7 +1227,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="2880000"/>
@@ -1222,7 +1249,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>134</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="2880000"/>
@@ -1271,8 +1298,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HistoryTable" displayName="HistoryTable" ref="A1:AS108" headerRowCount="1">
-  <autoFilter ref="A1:AS108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HistoryTable" displayName="HistoryTable" ref="A1:AS115" headerRowCount="1">
+  <autoFilter ref="A1:AS115"/>
   <tableColumns count="45">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="IRT_Mother_Gold"/>
@@ -1353,8 +1380,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TrendTable" displayName="TrendTable" ref="A1:J108" headerRowCount="1">
-  <autoFilter ref="A1:J108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TrendTable" displayName="TrendTable" ref="A1:J115" headerRowCount="1">
+  <autoFilter ref="A1:J115"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Total IRT"/>
@@ -1679,15 +1706,17 @@
   <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1716,12 +1745,12 @@
           <t>Total Net Worth (USD)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Latest Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>USD Rate</t>
         </is>
@@ -1729,17 +1758,17 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>24131985880</v>
+        <v>23987529210</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>138530.3437428244</v>
-      </c>
-      <c r="G5" s="5">
-        <f>History_Data!A108</f>
-        <v/>
-      </c>
-      <c r="J5" s="4">
-        <f>IFERROR(XLOOKUP("Tether",Live_Data!A:A,Live_Data!B:B),XLOOKUP("US Dollar",Live_Data!A:A,Live_Data!B:B))</f>
+        <v>124030.6577559462</v>
+      </c>
+      <c r="H5" s="5">
+        <f>History_Data!A115</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>Live_Data!B4</f>
         <v/>
       </c>
     </row>
@@ -1751,7 +1780,7 @@
           <t>Owner Split</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Latest Prices</t>
         </is>
@@ -1780,22 +1809,23 @@
       </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1804,24 +1834,24 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>11952480880</v>
+        <v>12172999210</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>68613.55269804822</v>
+        <v>62942.08485005171</v>
       </c>
       <c r="D10" s="10">
-        <f>IFERROR(B10/B5,0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="8">
+        <f>IFERROR(B10/A5,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="8">
         <f>Live_Data!A2</f>
         <v/>
       </c>
-      <c r="H10" s="8">
+      <c r="I10" s="8">
         <f>Live_Data!B2</f>
         <v/>
       </c>
-      <c r="I10" s="8">
+      <c r="J10" s="8">
         <f>Live_Data!C2</f>
         <v/>
       </c>
@@ -1833,52 +1863,52 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>12179505000</v>
+        <v>11814530000</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>69916.79104477612</v>
+        <v>61088.57290589451</v>
       </c>
       <c r="D11" s="10">
-        <f>IFERROR(B11/B5,0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="8">
+        <f>IFERROR(B11/A5,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="8">
         <f>Live_Data!A3</f>
         <v/>
       </c>
-      <c r="H11" s="8">
+      <c r="I11" s="8">
         <f>Live_Data!B3</f>
         <v/>
       </c>
-      <c r="I11" s="8">
+      <c r="J11" s="8">
         <f>Live_Data!C3</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="G12" s="8">
+      <c r="H12" s="8">
         <f>Live_Data!A4</f>
         <v/>
       </c>
-      <c r="H12" s="8">
+      <c r="I12" s="8">
         <f>Live_Data!B4</f>
         <v/>
       </c>
-      <c r="I12" s="8">
+      <c r="J12" s="8">
         <f>Live_Data!C4</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="G13" s="8">
+      <c r="H13" s="8">
         <f>Live_Data!A5</f>
         <v/>
       </c>
-      <c r="H13" s="8">
+      <c r="I13" s="8">
         <f>Live_Data!B5</f>
         <v/>
       </c>
-      <c r="I13" s="8">
+      <c r="J13" s="8">
         <f>Live_Data!C5</f>
         <v/>
       </c>
@@ -1889,15 +1919,15 @@
           <t>Asset-Class Allocation</t>
         </is>
       </c>
-      <c r="G14" s="8">
+      <c r="H14" s="8">
         <f>Live_Data!A6</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="I14" s="8">
         <f>Live_Data!B6</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="J14" s="8">
         <f>Live_Data!C6</f>
         <v/>
       </c>
@@ -1929,19 +1959,20 @@
         </is>
       </c>
       <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7">
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7">
         <f>Live_Data!A7</f>
         <v/>
       </c>
-      <c r="H15" s="7">
+      <c r="I15" s="7">
         <f>Live_Data!B7</f>
         <v/>
       </c>
-      <c r="I15" s="7">
+      <c r="J15" s="7">
         <f>Live_Data!C7</f>
         <v/>
       </c>
-      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1950,28 +1981,28 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>8151135880</v>
+        <v>8575129210</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>46791.82479908152</v>
+        <v>44338.82735263703</v>
       </c>
       <c r="D16" s="10">
-        <f>IFERROR(B16/B5,0)</f>
+        <f>IFERROR(B16/A5,0)</f>
         <v/>
       </c>
       <c r="E16" s="10">
         <f>IFERROR(C16/D5,0)</f>
         <v/>
       </c>
-      <c r="G16" s="8">
+      <c r="H16" s="8">
         <f>Live_Data!A8</f>
         <v/>
       </c>
-      <c r="H16" s="8">
+      <c r="I16" s="8">
         <f>Live_Data!B8</f>
         <v/>
       </c>
-      <c r="I16" s="8">
+      <c r="J16" s="8">
         <f>Live_Data!C8</f>
         <v/>
       </c>
@@ -1983,28 +2014,28 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>612850000</v>
+        <v>676900000</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>3518.082663605052</v>
+        <v>3500</v>
       </c>
       <c r="D17" s="10">
-        <f>IFERROR(B17/B5,0)</f>
+        <f>IFERROR(B17/A5,0)</f>
         <v/>
       </c>
       <c r="E17" s="10">
         <f>IFERROR(C17/D5,0)</f>
         <v/>
       </c>
-      <c r="G17" s="8">
+      <c r="H17" s="8">
         <f>Live_Data!A9</f>
         <v/>
       </c>
-      <c r="H17" s="8">
+      <c r="I17" s="8">
         <f>Live_Data!B9</f>
         <v/>
       </c>
-      <c r="I17" s="8">
+      <c r="J17" s="8">
         <f>Live_Data!C9</f>
         <v/>
       </c>
@@ -2016,28 +2047,28 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>7650000000</v>
+        <v>7017500000</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>43915.0401836969</v>
+        <v>36284.90175801448</v>
       </c>
       <c r="D18" s="10">
-        <f>IFERROR(B18/B5,0)</f>
+        <f>IFERROR(B18/A5,0)</f>
         <v/>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(C18/D5,0)</f>
         <v/>
       </c>
-      <c r="G18" s="8">
+      <c r="H18" s="8">
         <f>Live_Data!A10</f>
         <v/>
       </c>
-      <c r="H18" s="8">
+      <c r="I18" s="8">
         <f>Live_Data!B10</f>
         <v/>
       </c>
-      <c r="I18" s="8">
+      <c r="J18" s="8">
         <f>Live_Data!C10</f>
         <v/>
       </c>
@@ -2052,25 +2083,25 @@
         <v>7718000000</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>44305.39609644088</v>
+        <v>39906.92864529473</v>
       </c>
       <c r="D19" s="10">
-        <f>IFERROR(B19/B5,0)</f>
+        <f>IFERROR(B19/A5,0)</f>
         <v/>
       </c>
       <c r="E19" s="10">
         <f>IFERROR(C19/D5,0)</f>
         <v/>
       </c>
-      <c r="G19" s="8">
+      <c r="H19" s="8">
         <f>Live_Data!A11</f>
         <v/>
       </c>
-      <c r="H19" s="8">
+      <c r="I19" s="8">
         <f>Live_Data!B11</f>
         <v/>
       </c>
-      <c r="I19" s="8">
+      <c r="J19" s="8">
         <f>Live_Data!C11</f>
         <v/>
       </c>
@@ -2088,50 +2119,50 @@
         <v>0</v>
       </c>
       <c r="D20" s="10">
-        <f>IFERROR(B20/B5,0)</f>
+        <f>IFERROR(B20/A5,0)</f>
         <v/>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(C20/D5,0)</f>
         <v/>
       </c>
-      <c r="G20" s="8">
+      <c r="H20" s="8">
         <f>Live_Data!A12</f>
         <v/>
       </c>
-      <c r="H20" s="8">
+      <c r="I20" s="8">
         <f>Live_Data!B12</f>
         <v/>
       </c>
-      <c r="I20" s="8">
+      <c r="J20" s="8">
         <f>Live_Data!C12</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="G21" s="8">
+      <c r="H21" s="8">
         <f>Live_Data!A13</f>
         <v/>
       </c>
-      <c r="H21" s="8">
+      <c r="I21" s="8">
         <f>Live_Data!B13</f>
         <v/>
       </c>
-      <c r="I21" s="8">
+      <c r="J21" s="8">
         <f>Live_Data!C13</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="G22" s="8">
+      <c r="H22" s="8">
         <f>Live_Data!A14</f>
         <v/>
       </c>
-      <c r="H22" s="8">
+      <c r="I22" s="8">
         <f>Live_Data!B14</f>
         <v/>
       </c>
-      <c r="I22" s="8">
+      <c r="J22" s="8">
         <f>Live_Data!C14</f>
         <v/>
       </c>
@@ -2152,9 +2183,9 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2244,7 +2275,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46208.60150462963</v>
+        <v>46221.72034722222</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -2263,54 +2294,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS108"/>
+  <dimension ref="A1:AS115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="16" customWidth="1" min="30" max="30"/>
-    <col width="16" customWidth="1" min="31" max="31"/>
-    <col width="16" customWidth="1" min="32" max="32"/>
-    <col width="16" customWidth="1" min="33" max="33"/>
-    <col width="16" customWidth="1" min="34" max="34"/>
-    <col width="16" customWidth="1" min="35" max="35"/>
-    <col width="16" customWidth="1" min="36" max="36"/>
-    <col width="16" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="16" customWidth="1" min="39" max="39"/>
-    <col width="16" customWidth="1" min="40" max="40"/>
-    <col width="16" customWidth="1" min="41" max="41"/>
-    <col width="16" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
-    <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2590,28 +2621,28 @@
         <v>0</v>
       </c>
       <c r="Q2" s="9" t="n">
-        <v>28204.1468</v>
+        <v>27401.0692</v>
       </c>
       <c r="R2" s="9" t="n">
-        <v>500</v>
+        <v>485.7631</v>
       </c>
       <c r="S2" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T2" s="9" t="n">
-        <v>49206.248</v>
+        <v>47805.1621</v>
       </c>
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>27781.3197</v>
+        <v>26990.2816</v>
       </c>
       <c r="W2" s="9" t="n">
-        <v>3000</v>
+        <v>2914.5788</v>
       </c>
       <c r="X2" s="9" t="n">
-        <v>41903.0921</v>
+        <v>40709.9544</v>
       </c>
       <c r="Y2" s="9" t="n">
         <v>0</v>
@@ -2620,16 +2651,16 @@
         <v>0</v>
       </c>
       <c r="AA2" s="9" t="n">
-        <v>55985.4665</v>
+        <v>54391.3509</v>
       </c>
       <c r="AB2" s="9" t="n">
-        <v>3500</v>
+        <v>3400.3419</v>
       </c>
       <c r="AC2" s="9" t="n">
-        <v>41903.0921</v>
+        <v>40709.9544</v>
       </c>
       <c r="AD2" s="9" t="n">
-        <v>49206.248</v>
+        <v>47805.1621</v>
       </c>
       <c r="AE2" s="9" t="n">
         <v>0</v>
@@ -2638,7 +2669,7 @@
         <v>73000</v>
       </c>
       <c r="AG2" s="9" t="n">
-        <v>0</v>
+        <v>161447</v>
       </c>
       <c r="AH2" s="9" t="n">
         <v>156850</v>
@@ -2727,28 +2758,28 @@
         <v>0</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>27501.1595</v>
+        <v>27315.2142</v>
       </c>
       <c r="R3" s="9" t="n">
-        <v>500</v>
+        <v>496.6193</v>
       </c>
       <c r="S3" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T3" s="9" t="n">
-        <v>47565.801</v>
+        <v>47244.1909</v>
       </c>
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>27107.2063</v>
+        <v>26923.9313</v>
       </c>
       <c r="W3" s="9" t="n">
-        <v>3000</v>
+        <v>2979.7161</v>
       </c>
       <c r="X3" s="9" t="n">
-        <v>40506.1191</v>
+        <v>40232.2421</v>
       </c>
       <c r="Y3" s="9" t="n">
         <v>0</v>
@@ -2757,16 +2788,16 @@
         <v>0</v>
       </c>
       <c r="AA3" s="9" t="n">
-        <v>54608.3659</v>
+        <v>54239.1455</v>
       </c>
       <c r="AB3" s="9" t="n">
-        <v>3500</v>
+        <v>3476.3354</v>
       </c>
       <c r="AC3" s="9" t="n">
-        <v>40506.1191</v>
+        <v>40232.2421</v>
       </c>
       <c r="AD3" s="9" t="n">
-        <v>47565.801</v>
+        <v>47244.1909</v>
       </c>
       <c r="AE3" s="9" t="n">
         <v>0</v>
@@ -2775,7 +2806,7 @@
         <v>69515.19560000001</v>
       </c>
       <c r="AG3" s="9" t="n">
-        <v>0</v>
+        <v>163364</v>
       </c>
       <c r="AH3" s="9" t="n">
         <v>162259.4444</v>
@@ -2819,7 +2850,7 @@
         <v>46059</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>4413002936</v>
+        <v>4413420936</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>81120000</v>
@@ -2849,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>8788402936</v>
+        <v>8788820936</v>
       </c>
       <c r="M4" s="9" t="n">
         <v>567840000</v>
@@ -2864,28 +2895,28 @@
         <v>0</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>27200.4619</v>
+        <v>26857.8788</v>
       </c>
       <c r="R4" s="9" t="n">
-        <v>500</v>
+        <v>493.6559</v>
       </c>
       <c r="S4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T4" s="9" t="n">
-        <v>47571.499</v>
+        <v>46967.899</v>
       </c>
       <c r="U4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>26968.6884</v>
+        <v>26626.5024</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>3000</v>
+        <v>2961.9352</v>
       </c>
       <c r="X4" s="9" t="n">
-        <v>40510.9714</v>
+        <v>39996.9572</v>
       </c>
       <c r="Y4" s="9" t="n">
         <v>0</v>
@@ -2894,25 +2925,25 @@
         <v>0</v>
       </c>
       <c r="AA4" s="9" t="n">
-        <v>54169.1502</v>
+        <v>53484.3812</v>
       </c>
       <c r="AB4" s="9" t="n">
-        <v>3500</v>
+        <v>3455.5911</v>
       </c>
       <c r="AC4" s="9" t="n">
-        <v>40510.9714</v>
+        <v>39996.9572</v>
       </c>
       <c r="AD4" s="9" t="n">
-        <v>47571.499</v>
+        <v>46967.899</v>
       </c>
       <c r="AE4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF4" s="9" t="n">
-        <v>68013.1776</v>
+        <v>67939.8707</v>
       </c>
       <c r="AG4" s="9" t="n">
-        <v>0</v>
+        <v>164325</v>
       </c>
       <c r="AH4" s="9" t="n">
         <v>162240</v>
@@ -2939,7 +2970,7 @@
         <v>27500000</v>
       </c>
       <c r="AP4" s="9" t="n">
-        <v>19064300</v>
+        <v>19066833.3333</v>
       </c>
       <c r="AQ4" s="9" t="n">
         <v>2629</v>
@@ -2948,7 +2979,7 @@
         <v>191560</v>
       </c>
       <c r="AS4" s="9" t="n">
-        <v>4939.4118</v>
+        <v>4938.2667</v>
       </c>
     </row>
     <row r="5">
@@ -2956,10 +2987,10 @@
         <v>46060</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>4318932058.4444</v>
+        <v>4332152947.3333</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>78911388.8889</v>
+        <v>79289166.66670001</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>0</v>
@@ -2971,10 +3002,10 @@
         <v>0</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>4218513333.3333</v>
+        <v>4227730000</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>473468333.3333</v>
+        <v>475735000</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>6720000000</v>
@@ -2986,10 +3017,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>8537445391.7778</v>
+        <v>8559882947.3333</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>552379722.2222</v>
+        <v>555024166.6667</v>
       </c>
       <c r="N5" s="9" t="n">
         <v>6720000000</v>
@@ -3001,28 +3032,28 @@
         <v>0</v>
       </c>
       <c r="Q5" s="9" t="n">
-        <v>27365.9048</v>
+        <v>26860.2347</v>
       </c>
       <c r="R5" s="9" t="n">
-        <v>500</v>
+        <v>491.6091</v>
       </c>
       <c r="S5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T5" s="9" t="n">
-        <v>48903.9287</v>
+        <v>47853.1792</v>
       </c>
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>26729.7226</v>
+        <v>26212.791</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>3000</v>
+        <v>2949.6543</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>42580.2541</v>
+        <v>41665.375</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -3031,16 +3062,16 @@
         <v>0</v>
       </c>
       <c r="AA5" s="9" t="n">
-        <v>54095.6274</v>
+        <v>53073.0257</v>
       </c>
       <c r="AB5" s="9" t="n">
-        <v>3500</v>
+        <v>3441.2634</v>
       </c>
       <c r="AC5" s="9" t="n">
-        <v>42580.2541</v>
+        <v>41665.375</v>
       </c>
       <c r="AD5" s="9" t="n">
-        <v>48903.9287</v>
+        <v>47853.1792</v>
       </c>
       <c r="AE5" s="9" t="n">
         <v>0</v>
@@ -3049,13 +3080,13 @@
         <v>68078.52</v>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>0</v>
+        <v>161285</v>
       </c>
       <c r="AH5" s="9" t="n">
-        <v>157822.7778</v>
+        <v>158578.3333</v>
       </c>
       <c r="AI5" s="9" t="n">
-        <v>188224444.4444</v>
+        <v>188663333.3333</v>
       </c>
       <c r="AJ5" s="9" t="n">
         <v>99300000</v>
@@ -3076,13 +3107,13 @@
         <v>26500000</v>
       </c>
       <c r="AP5" s="9" t="n">
-        <v>18621533.3333</v>
+        <v>18699000</v>
       </c>
       <c r="AQ5" s="9" t="n">
         <v>2688</v>
       </c>
       <c r="AR5" s="9" t="n">
-        <v>186532.2222</v>
+        <v>187436.6667</v>
       </c>
       <c r="AS5" s="9" t="n">
         <v>4961</v>
@@ -3093,10 +3124,10 @@
         <v>46061</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>4264522753.3333</v>
+        <v>4309543924</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>78405000</v>
+        <v>78675000</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>0</v>
@@ -3108,10 +3139,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>4202796666.6667</v>
+        <v>4214105000</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>470430000</v>
+        <v>472050000</v>
       </c>
       <c r="I6" s="9" t="n">
         <v>6515000000</v>
@@ -3123,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>8467319420</v>
+        <v>8523648924</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>548835000</v>
+        <v>550725000</v>
       </c>
       <c r="N6" s="9" t="n">
         <v>6515000000</v>
@@ -3138,28 +3169,28 @@
         <v>0</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>27194.8858</v>
+        <v>26854.7566</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>500</v>
+        <v>490.2602</v>
       </c>
       <c r="S6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>49223.3526</v>
+        <v>48094.4191</v>
       </c>
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>26802.4524</v>
+        <v>26260.0327</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>3000</v>
+        <v>2941.5614</v>
       </c>
       <c r="X6" s="9" t="n">
-        <v>41550.9384</v>
+        <v>40597.971</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>0</v>
@@ -3168,40 +3199,40 @@
         <v>0</v>
       </c>
       <c r="AA6" s="9" t="n">
-        <v>53997.3382</v>
+        <v>53114.7893</v>
       </c>
       <c r="AB6" s="9" t="n">
-        <v>3500</v>
+        <v>3431.8216</v>
       </c>
       <c r="AC6" s="9" t="n">
-        <v>41550.9384</v>
+        <v>40597.971</v>
       </c>
       <c r="AD6" s="9" t="n">
-        <v>49223.3526</v>
+        <v>48094.4191</v>
       </c>
       <c r="AE6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF6" s="9" t="n">
-        <v>70557.65670000001</v>
+        <v>70669.86</v>
       </c>
       <c r="AG6" s="9" t="n">
-        <v>0</v>
+        <v>160476</v>
       </c>
       <c r="AH6" s="9" t="n">
-        <v>156810</v>
+        <v>157350</v>
       </c>
       <c r="AI6" s="9" t="n">
-        <v>187886666.6667</v>
+        <v>188340000</v>
       </c>
       <c r="AJ6" s="9" t="n">
-        <v>95766666.66670001</v>
+        <v>95900000</v>
       </c>
       <c r="AK6" s="9" t="n">
-        <v>53803333.3333</v>
+        <v>54355000</v>
       </c>
       <c r="AL6" s="9" t="n">
-        <v>46777206</v>
+        <v>47256831</v>
       </c>
       <c r="AM6" s="9" t="n">
         <v>25900000</v>
@@ -3210,16 +3241,16 @@
         <v>61610000</v>
       </c>
       <c r="AO6" s="9" t="n">
-        <v>17891252</v>
+        <v>26836878</v>
       </c>
       <c r="AP6" s="9" t="n">
-        <v>18602666.6667</v>
+        <v>18623350</v>
       </c>
       <c r="AQ6" s="9" t="n">
         <v>2606</v>
       </c>
       <c r="AR6" s="9" t="n">
-        <v>185350</v>
+        <v>185985</v>
       </c>
       <c r="AS6" s="9" t="n">
         <v>4961</v>
@@ -3275,28 +3306,28 @@
         <v>0</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>27485.5584</v>
+        <v>27013.3088</v>
       </c>
       <c r="R7" s="9" t="n">
-        <v>500</v>
+        <v>491.3893</v>
       </c>
       <c r="S7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>48057.9117</v>
+        <v>47227.7125</v>
       </c>
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>26974.5921</v>
+        <v>26511.4949</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>3000</v>
+        <v>2948.3359</v>
       </c>
       <c r="X7" s="9" t="n">
-        <v>40288.4036</v>
+        <v>39590.995</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>0</v>
@@ -3305,16 +3336,16 @@
         <v>0</v>
       </c>
       <c r="AA7" s="9" t="n">
-        <v>54460.1504</v>
+        <v>53524.8036</v>
       </c>
       <c r="AB7" s="9" t="n">
-        <v>3500</v>
+        <v>3439.7252</v>
       </c>
       <c r="AC7" s="9" t="n">
-        <v>40288.4036</v>
+        <v>39590.995</v>
       </c>
       <c r="AD7" s="9" t="n">
-        <v>48057.9117</v>
+        <v>47227.7125</v>
       </c>
       <c r="AE7" s="9" t="n">
         <v>0</v>
@@ -3323,7 +3354,7 @@
         <v>69888.14</v>
       </c>
       <c r="AG7" s="9" t="n">
-        <v>0</v>
+        <v>163421</v>
       </c>
       <c r="AH7" s="9" t="n">
         <v>160606.6667</v>
@@ -3412,28 +3443,28 @@
         <v>0</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>28000.688</v>
+        <v>27660.4244</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>500</v>
+        <v>493.9202</v>
       </c>
       <c r="S8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>47360.0111</v>
+        <v>46783.6966</v>
       </c>
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>27403.0316</v>
+        <v>27070.0786</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>3000</v>
+        <v>2963.5211</v>
       </c>
       <c r="X8" s="9" t="n">
-        <v>38689.3119</v>
+        <v>38218.6068</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>0</v>
@@ -3442,16 +3473,16 @@
         <v>0</v>
       </c>
       <c r="AA8" s="9" t="n">
-        <v>55403.7196</v>
+        <v>54730.503</v>
       </c>
       <c r="AB8" s="9" t="n">
-        <v>3500</v>
+        <v>3457.4413</v>
       </c>
       <c r="AC8" s="9" t="n">
-        <v>38689.3119</v>
+        <v>38218.6068</v>
       </c>
       <c r="AD8" s="9" t="n">
-        <v>47360.0111</v>
+        <v>46783.6966</v>
       </c>
       <c r="AE8" s="9" t="n">
         <v>0</v>
@@ -3460,7 +3491,7 @@
         <v>69115.728</v>
       </c>
       <c r="AG8" s="9" t="n">
-        <v>0</v>
+        <v>164972</v>
       </c>
       <c r="AH8" s="9" t="n">
         <v>162966</v>
@@ -3549,28 +3580,28 @@
         <v>0</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>27977.9144</v>
+        <v>27600.5291</v>
       </c>
       <c r="R9" s="9" t="n">
-        <v>500</v>
+        <v>493.2557</v>
       </c>
       <c r="S9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="9" t="n">
-        <v>47280.0784</v>
+        <v>46642.3322</v>
       </c>
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>27397.8192</v>
+        <v>27028.2586</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>3000</v>
+        <v>2959.5339</v>
       </c>
       <c r="X9" s="9" t="n">
-        <v>38593.482</v>
+        <v>38072.9066</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
@@ -3579,16 +3610,16 @@
         <v>0</v>
       </c>
       <c r="AA9" s="9" t="n">
-        <v>55375.7336</v>
+        <v>54628.7876</v>
       </c>
       <c r="AB9" s="9" t="n">
-        <v>3500</v>
+        <v>3452.7896</v>
       </c>
       <c r="AC9" s="9" t="n">
-        <v>38593.482</v>
+        <v>38072.9066</v>
       </c>
       <c r="AD9" s="9" t="n">
-        <v>47280.0784</v>
+        <v>46642.3322</v>
       </c>
       <c r="AE9" s="9" t="n">
         <v>0</v>
@@ -3597,7 +3628,7 @@
         <v>67067.9633</v>
       </c>
       <c r="AG9" s="9" t="n">
-        <v>0</v>
+        <v>165472</v>
       </c>
       <c r="AH9" s="9" t="n">
         <v>163240</v>
@@ -3641,10 +3672,10 @@
         <v>46065</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>4481018829.6</v>
+        <v>4481812542.5</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>81129000</v>
+        <v>81145000</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>0</v>
@@ -3656,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>4391342000</v>
+        <v>4393588750</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>486774000</v>
+        <v>486870000</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>6300000000</v>
@@ -3671,10 +3702,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>8872360829.6</v>
+        <v>8875401292.5</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>567903000</v>
+        <v>568015000</v>
       </c>
       <c r="N10" s="9" t="n">
         <v>6300000000</v>
@@ -3686,28 +3717,28 @@
         <v>0</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>27616.6874</v>
+        <v>27322.4608</v>
       </c>
       <c r="R10" s="9" t="n">
-        <v>500</v>
+        <v>494.684</v>
       </c>
       <c r="S10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>47566.2935</v>
+        <v>47051.2211</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>27064.0672</v>
+        <v>26784.6224</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>3000</v>
+        <v>2968.1042</v>
       </c>
       <c r="X10" s="9" t="n">
-        <v>38827.1118</v>
+        <v>38406.6718</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -3716,40 +3747,40 @@
         <v>0</v>
       </c>
       <c r="AA10" s="9" t="n">
-        <v>54680.7546</v>
+        <v>54107.0832</v>
       </c>
       <c r="AB10" s="9" t="n">
-        <v>3500</v>
+        <v>3462.7882</v>
       </c>
       <c r="AC10" s="9" t="n">
-        <v>38827.1118</v>
+        <v>38406.6718</v>
       </c>
       <c r="AD10" s="9" t="n">
-        <v>47566.2935</v>
+        <v>47051.2211</v>
       </c>
       <c r="AE10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF10" s="9" t="n">
-        <v>67143.61199999999</v>
+        <v>66979.535</v>
       </c>
       <c r="AG10" s="9" t="n">
-        <v>0</v>
+        <v>164034</v>
       </c>
       <c r="AH10" s="9" t="n">
-        <v>162258</v>
+        <v>162290</v>
       </c>
       <c r="AI10" s="9" t="n">
-        <v>196404000</v>
+        <v>196503750</v>
       </c>
       <c r="AJ10" s="9" t="n">
-        <v>99074000</v>
+        <v>99182500</v>
       </c>
       <c r="AK10" s="9" t="n">
-        <v>55928000</v>
+        <v>55942500</v>
       </c>
       <c r="AL10" s="9" t="n">
-        <v>48624414.8</v>
+        <v>48637021.25</v>
       </c>
       <c r="AM10" s="9" t="n">
         <v>25900000</v>
@@ -3761,16 +3792,16 @@
         <v>27500000</v>
       </c>
       <c r="AP10" s="9" t="n">
-        <v>19504800</v>
+        <v>19508150</v>
       </c>
       <c r="AQ10" s="9" t="n">
         <v>2520</v>
       </c>
       <c r="AR10" s="9" t="n">
-        <v>192834</v>
+        <v>192852.5</v>
       </c>
       <c r="AS10" s="9" t="n">
-        <v>5040.6</v>
+        <v>5035.25</v>
       </c>
     </row>
     <row r="11">
@@ -3823,28 +3854,28 @@
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>27576.0866</v>
+        <v>27480.3997</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>500</v>
+        <v>498.265</v>
       </c>
       <c r="S11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>47480.7751</v>
+        <v>47316.0205</v>
       </c>
       <c r="U11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>26954.9677</v>
+        <v>26861.436</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>3000</v>
+        <v>2989.5902</v>
       </c>
       <c r="X11" s="9" t="n">
-        <v>38757.3054</v>
+        <v>38622.8206</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>0</v>
@@ -3853,16 +3884,16 @@
         <v>0</v>
       </c>
       <c r="AA11" s="9" t="n">
-        <v>54531.0543</v>
+        <v>54341.8357</v>
       </c>
       <c r="AB11" s="9" t="n">
-        <v>3500</v>
+        <v>3487.8553</v>
       </c>
       <c r="AC11" s="9" t="n">
-        <v>38757.3054</v>
+        <v>38622.8206</v>
       </c>
       <c r="AD11" s="9" t="n">
-        <v>47480.7751</v>
+        <v>47316.0205</v>
       </c>
       <c r="AE11" s="9" t="n">
         <v>0</v>
@@ -3871,7 +3902,7 @@
         <v>67727.465</v>
       </c>
       <c r="AG11" s="9" t="n">
-        <v>0</v>
+        <v>163116</v>
       </c>
       <c r="AH11" s="9" t="n">
         <v>162550</v>
@@ -3960,28 +3991,28 @@
         <v>0</v>
       </c>
       <c r="Q12" s="9" t="n">
-        <v>27202.4414</v>
+        <v>26807.0893</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>500</v>
+        <v>492.7313</v>
       </c>
       <c r="S12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>48655.7411</v>
+        <v>47948.3117</v>
       </c>
       <c r="U12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>26922.0814</v>
+        <v>26530.6588</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>3000</v>
+        <v>2956.388</v>
       </c>
       <c r="X12" s="9" t="n">
-        <v>38613.1659</v>
+        <v>38051.7504</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
@@ -3990,16 +4021,16 @@
         <v>0</v>
       </c>
       <c r="AA12" s="9" t="n">
-        <v>54124.5228</v>
+        <v>53337.7481</v>
       </c>
       <c r="AB12" s="9" t="n">
-        <v>3500</v>
+        <v>3449.1194</v>
       </c>
       <c r="AC12" s="9" t="n">
-        <v>38613.1659</v>
+        <v>38051.7504</v>
       </c>
       <c r="AD12" s="9" t="n">
-        <v>48655.7411</v>
+        <v>47948.3117</v>
       </c>
       <c r="AE12" s="9" t="n">
         <v>0</v>
@@ -4008,7 +4039,7 @@
         <v>69627.00999999999</v>
       </c>
       <c r="AG12" s="9" t="n">
-        <v>0</v>
+        <v>160965</v>
       </c>
       <c r="AH12" s="9" t="n">
         <v>158625</v>
@@ -4097,28 +4128,28 @@
         <v>0</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>27481.7854</v>
+        <v>27297.6661</v>
       </c>
       <c r="R13" s="9" t="n">
-        <v>500</v>
+        <v>496.6345</v>
       </c>
       <c r="S13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>48417.4561</v>
+        <v>48090.5233</v>
       </c>
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>27226.0765</v>
+        <v>27043.4344</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>3000</v>
+        <v>2979.807</v>
       </c>
       <c r="X13" s="9" t="n">
-        <v>38388.851</v>
+        <v>38129.5603</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>0</v>
@@ -4127,16 +4158,16 @@
         <v>0</v>
       </c>
       <c r="AA13" s="9" t="n">
-        <v>54707.8619</v>
+        <v>54341.1005</v>
       </c>
       <c r="AB13" s="9" t="n">
-        <v>3500</v>
+        <v>3476.4415</v>
       </c>
       <c r="AC13" s="9" t="n">
-        <v>38388.851</v>
+        <v>38129.5603</v>
       </c>
       <c r="AD13" s="9" t="n">
-        <v>48417.4561</v>
+        <v>48090.5233</v>
       </c>
       <c r="AE13" s="9" t="n">
         <v>0</v>
@@ -4145,7 +4176,7 @@
         <v>69855.08500000001</v>
       </c>
       <c r="AG13" s="9" t="n">
-        <v>0</v>
+        <v>160489</v>
       </c>
       <c r="AH13" s="9" t="n">
         <v>159408.75</v>
@@ -4234,28 +4265,28 @@
         <v>0</v>
       </c>
       <c r="Q14" s="9" t="n">
-        <v>27438.5903</v>
+        <v>27213.7582</v>
       </c>
       <c r="R14" s="9" t="n">
-        <v>500</v>
+        <v>495.9059</v>
       </c>
       <c r="S14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="9" t="n">
-        <v>48283.2852</v>
+        <v>47887.9182</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>27137.5803</v>
+        <v>26915.2272</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>3000</v>
+        <v>2975.4356</v>
       </c>
       <c r="X14" s="9" t="n">
-        <v>39073.213</v>
+        <v>38753.5574</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
@@ -4264,16 +4295,16 @@
         <v>0</v>
       </c>
       <c r="AA14" s="9" t="n">
-        <v>54576.1706</v>
+        <v>54128.9854</v>
       </c>
       <c r="AB14" s="9" t="n">
-        <v>3500</v>
+        <v>3471.3415</v>
       </c>
       <c r="AC14" s="9" t="n">
-        <v>39073.213</v>
+        <v>38753.5574</v>
       </c>
       <c r="AD14" s="9" t="n">
-        <v>48283.2852</v>
+        <v>47887.9182</v>
       </c>
       <c r="AE14" s="9" t="n">
         <v>0</v>
@@ -4282,7 +4313,7 @@
         <v>68412.07000000001</v>
       </c>
       <c r="AG14" s="9" t="n">
-        <v>0</v>
+        <v>161168</v>
       </c>
       <c r="AH14" s="9" t="n">
         <v>159848.3333</v>
@@ -4371,28 +4402,28 @@
         <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>27192.244</v>
+        <v>27145.9328</v>
       </c>
       <c r="R15" s="9" t="n">
-        <v>500</v>
+        <v>499.1433</v>
       </c>
       <c r="S15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="9" t="n">
-        <v>47824.0932</v>
+        <v>47741.5843</v>
       </c>
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>27142.7796</v>
+        <v>27095.978</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>3000</v>
+        <v>2994.8596</v>
       </c>
       <c r="X15" s="9" t="n">
-        <v>40075.4499</v>
+        <v>40006.3095</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -4401,16 +4432,16 @@
         <v>0</v>
       </c>
       <c r="AA15" s="9" t="n">
-        <v>54335.0236</v>
+        <v>54241.9108</v>
       </c>
       <c r="AB15" s="9" t="n">
-        <v>3500</v>
+        <v>3494.0029</v>
       </c>
       <c r="AC15" s="9" t="n">
-        <v>40075.4499</v>
+        <v>40006.3095</v>
       </c>
       <c r="AD15" s="9" t="n">
-        <v>47824.0932</v>
+        <v>47741.5843</v>
       </c>
       <c r="AE15" s="9" t="n">
         <v>0</v>
@@ -4419,7 +4450,7 @@
         <v>67987.98</v>
       </c>
       <c r="AG15" s="9" t="n">
-        <v>0</v>
+        <v>161662</v>
       </c>
       <c r="AH15" s="9" t="n">
         <v>161385</v>
@@ -4508,28 +4539,28 @@
         <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>27676.4432</v>
+        <v>27316.6024</v>
       </c>
       <c r="R16" s="9" t="n">
-        <v>500</v>
+        <v>493.4923</v>
       </c>
       <c r="S16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="9" t="n">
-        <v>47448.8167</v>
+        <v>46831.1034</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>27138.939</v>
+        <v>26786.1109</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>3000</v>
+        <v>2960.9539</v>
       </c>
       <c r="X16" s="9" t="n">
-        <v>39591.9124</v>
+        <v>39076.4843</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
@@ -4538,16 +4569,16 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="n">
-        <v>54815.3821</v>
+        <v>54102.7132</v>
       </c>
       <c r="AB16" s="9" t="n">
-        <v>3500</v>
+        <v>3454.4462</v>
       </c>
       <c r="AC16" s="9" t="n">
-        <v>39591.9124</v>
+        <v>39076.4843</v>
       </c>
       <c r="AD16" s="9" t="n">
-        <v>47448.8167</v>
+        <v>46831.1034</v>
       </c>
       <c r="AE16" s="9" t="n">
         <v>0</v>
@@ -4556,7 +4587,7 @@
         <v>66717.715</v>
       </c>
       <c r="AG16" s="9" t="n">
-        <v>0</v>
+        <v>164805</v>
       </c>
       <c r="AH16" s="9" t="n">
         <v>162660</v>
@@ -4645,28 +4676,28 @@
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>27840.1677</v>
+        <v>27537.431</v>
       </c>
       <c r="R17" s="9" t="n">
-        <v>500</v>
+        <v>494.563</v>
       </c>
       <c r="S17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="9" t="n">
-        <v>47164.5075</v>
+        <v>46651.636</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>27457.2232</v>
+        <v>27158.6506</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>3000</v>
+        <v>2967.3777</v>
       </c>
       <c r="X17" s="9" t="n">
-        <v>39354.681</v>
+        <v>38926.7343</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>0</v>
@@ -4675,16 +4706,16 @@
         <v>0</v>
       </c>
       <c r="AA17" s="9" t="n">
-        <v>55297.3909</v>
+        <v>54696.0816</v>
       </c>
       <c r="AB17" s="9" t="n">
-        <v>3500</v>
+        <v>3461.9407</v>
       </c>
       <c r="AC17" s="9" t="n">
-        <v>39354.681</v>
+        <v>38926.7343</v>
       </c>
       <c r="AD17" s="9" t="n">
-        <v>47164.5075</v>
+        <v>46651.636</v>
       </c>
       <c r="AE17" s="9" t="n">
         <v>0</v>
@@ -4693,7 +4724,7 @@
         <v>67558.31</v>
       </c>
       <c r="AG17" s="9" t="n">
-        <v>0</v>
+        <v>165439</v>
       </c>
       <c r="AH17" s="9" t="n">
         <v>163640</v>
@@ -4782,28 +4813,28 @@
         <v>0</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>27643.6265</v>
+        <v>27266.2816</v>
       </c>
       <c r="R18" s="9" t="n">
-        <v>500</v>
+        <v>493.1749</v>
       </c>
       <c r="S18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="9" t="n">
-        <v>47146.8373</v>
+        <v>46502.9403</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>27319.5102</v>
+        <v>26946.4144</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>3000</v>
+        <v>2959.0493</v>
       </c>
       <c r="X18" s="9" t="n">
-        <v>37339.3422</v>
+        <v>36829.3888</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
@@ -4812,16 +4843,16 @@
         <v>0</v>
       </c>
       <c r="AA18" s="9" t="n">
-        <v>54963.1367</v>
+        <v>54212.696</v>
       </c>
       <c r="AB18" s="9" t="n">
-        <v>3500</v>
+        <v>3452.2242</v>
       </c>
       <c r="AC18" s="9" t="n">
-        <v>37339.3422</v>
+        <v>36829.3888</v>
       </c>
       <c r="AD18" s="9" t="n">
-        <v>47146.8373</v>
+        <v>46502.9403</v>
       </c>
       <c r="AE18" s="9" t="n">
         <v>0</v>
@@ -4830,7 +4861,7 @@
         <v>67638.565</v>
       </c>
       <c r="AG18" s="9" t="n">
-        <v>0</v>
+        <v>165968</v>
       </c>
       <c r="AH18" s="9" t="n">
         <v>163702.5</v>
@@ -4874,10 +4905,10 @@
         <v>46077</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>3728290436.4</v>
+        <v>4557542648.6667</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>74522000</v>
+        <v>81879166.66670001</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>0</v>
@@ -4889,13 +4920,13 @@
         <v>0</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>3582429000</v>
+        <v>4472998333.3333</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>447132000</v>
+        <v>491275000</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>7375000000</v>
+        <v>6104166666.6667</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>0</v>
@@ -4904,13 +4935,13 @@
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>7310719436.4</v>
+        <v>9030540982</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>521654000</v>
+        <v>573154166.6667</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>7375000000</v>
+        <v>6104166666.6667</v>
       </c>
       <c r="O19" s="9" t="n">
         <v>7718000000</v>
@@ -4919,28 +4950,28 @@
         <v>0</v>
       </c>
       <c r="Q19" s="9" t="n">
-        <v>23189.9154</v>
+        <v>27512.9196</v>
       </c>
       <c r="R19" s="9" t="n">
-        <v>500</v>
+        <v>494.2872</v>
       </c>
       <c r="S19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>54844.7645</v>
+        <v>46591.9312</v>
       </c>
       <c r="U19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>21892.3975</v>
+        <v>27002.5435</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>3000</v>
+        <v>2965.7231</v>
       </c>
       <c r="X19" s="9" t="n">
-        <v>57539.1295</v>
+        <v>36849.5612</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
@@ -4949,40 +4980,40 @@
         <v>0</v>
       </c>
       <c r="AA19" s="9" t="n">
-        <v>45082.3129</v>
+        <v>54515.4631</v>
       </c>
       <c r="AB19" s="9" t="n">
-        <v>3500</v>
+        <v>3460.0103</v>
       </c>
       <c r="AC19" s="9" t="n">
-        <v>57539.1295</v>
+        <v>36849.5612</v>
       </c>
       <c r="AD19" s="9" t="n">
-        <v>54844.7645</v>
+        <v>46591.9312</v>
       </c>
       <c r="AE19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF19" s="9" t="n">
-        <v>63340.306</v>
+        <v>64066.9367</v>
       </c>
       <c r="AG19" s="9" t="n">
-        <v>0</v>
+        <v>165651</v>
       </c>
       <c r="AH19" s="9" t="n">
-        <v>149044</v>
+        <v>163758.3333</v>
       </c>
       <c r="AI19" s="9" t="n">
-        <v>160203000</v>
+        <v>200001666.6667</v>
       </c>
       <c r="AJ19" s="9" t="n">
-        <v>82386000</v>
+        <v>103073333.3333</v>
       </c>
       <c r="AK19" s="9" t="n">
-        <v>45260000</v>
+        <v>56630000</v>
       </c>
       <c r="AL19" s="9" t="n">
-        <v>39350068.2</v>
+        <v>49234741</v>
       </c>
       <c r="AM19" s="9" t="n">
         <v>25900000</v>
@@ -4991,19 +5022,19 @@
         <v>61610000</v>
       </c>
       <c r="AO19" s="9" t="n">
-        <v>22824000</v>
+        <v>28500000</v>
       </c>
       <c r="AP19" s="9" t="n">
-        <v>15905220</v>
+        <v>19881100</v>
       </c>
       <c r="AQ19" s="9" t="n">
-        <v>2950</v>
+        <v>2441.6667</v>
       </c>
       <c r="AR19" s="9" t="n">
-        <v>173498</v>
+        <v>193080</v>
       </c>
       <c r="AS19" s="9" t="n">
-        <v>4543.2</v>
+        <v>5186.3333</v>
       </c>
     </row>
     <row r="20">
@@ -5011,10 +5042,10 @@
         <v>46078</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>4600937679.25</v>
+        <v>4596867752.2857</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>82292187.5</v>
+        <v>82274285.71430001</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>0</v>
@@ -5026,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>4508901875</v>
+        <v>4507260000</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>493753125</v>
+        <v>493645714.2857</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>6138437500</v>
+        <v>6130357142.8571</v>
       </c>
       <c r="J20" s="9" t="n">
         <v>0</v>
@@ -5041,13 +5072,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>9109839554.25</v>
+        <v>9104127752.2857</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>576045312.5</v>
+        <v>575920000</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>6138437500</v>
+        <v>6130357142.8571</v>
       </c>
       <c r="O20" s="9" t="n">
         <v>7718000000</v>
@@ -5056,28 +5087,28 @@
         <v>0</v>
       </c>
       <c r="Q20" s="9" t="n">
-        <v>27954.2562</v>
+        <v>27602.5157</v>
       </c>
       <c r="R20" s="9" t="n">
-        <v>500</v>
+        <v>494.0271</v>
       </c>
       <c r="S20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="9" t="n">
-        <v>46894.3298</v>
+        <v>46343.7774</v>
       </c>
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>27395.37</v>
+        <v>27064.4538</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>3000</v>
+        <v>2964.1626</v>
       </c>
       <c r="X20" s="9" t="n">
-        <v>37295.8422</v>
+        <v>36810.5606</v>
       </c>
       <c r="Y20" s="9" t="n">
         <v>0</v>
@@ -5086,40 +5117,40 @@
         <v>0</v>
       </c>
       <c r="AA20" s="9" t="n">
-        <v>55349.6262</v>
+        <v>54666.9694</v>
       </c>
       <c r="AB20" s="9" t="n">
-        <v>3500</v>
+        <v>3458.1897</v>
       </c>
       <c r="AC20" s="9" t="n">
-        <v>37295.8422</v>
+        <v>36810.5606</v>
       </c>
       <c r="AD20" s="9" t="n">
-        <v>46894.3298</v>
+        <v>46343.7774</v>
       </c>
       <c r="AE20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF20" s="9" t="n">
-        <v>65159.9563</v>
+        <v>65197.0929</v>
       </c>
       <c r="AG20" s="9" t="n">
-        <v>0</v>
+        <v>166538</v>
       </c>
       <c r="AH20" s="9" t="n">
-        <v>164584.375</v>
+        <v>164548.5714</v>
       </c>
       <c r="AI20" s="9" t="n">
-        <v>201568125</v>
+        <v>201507142.8571</v>
       </c>
       <c r="AJ20" s="9" t="n">
-        <v>103718750</v>
+        <v>103607142.8571</v>
       </c>
       <c r="AK20" s="9" t="n">
-        <v>57417500</v>
+        <v>57334285.7143</v>
       </c>
       <c r="AL20" s="9" t="n">
-        <v>49919402.125</v>
+        <v>49847054.7143</v>
       </c>
       <c r="AM20" s="9" t="n">
         <v>25900000</v>
@@ -5128,19 +5159,19 @@
         <v>61610000</v>
       </c>
       <c r="AO20" s="9" t="n">
-        <v>28812500</v>
+        <v>28785714.2857</v>
       </c>
       <c r="AP20" s="9" t="n">
-        <v>20080550</v>
+        <v>20061814.2857</v>
       </c>
       <c r="AQ20" s="9" t="n">
-        <v>2455.375</v>
+        <v>2452.1429</v>
       </c>
       <c r="AR20" s="9" t="n">
-        <v>194116.25</v>
+        <v>194061.4286</v>
       </c>
       <c r="AS20" s="9" t="n">
-        <v>5169.75</v>
+        <v>5167.2857</v>
       </c>
     </row>
     <row r="21">
@@ -5193,28 +5224,28 @@
         <v>0</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>27993.1424</v>
+        <v>27891.2305</v>
       </c>
       <c r="R21" s="9" t="n">
-        <v>500</v>
+        <v>498.1799</v>
       </c>
       <c r="S21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="9" t="n">
-        <v>46735.6315</v>
+        <v>46565.5073</v>
       </c>
       <c r="U21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>27457.8605</v>
+        <v>27357.8992</v>
       </c>
       <c r="W21" s="9" t="n">
-        <v>3000</v>
+        <v>2989.0796</v>
       </c>
       <c r="X21" s="9" t="n">
-        <v>37543.5236</v>
+        <v>37406.8599</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
@@ -5223,16 +5254,16 @@
         <v>0</v>
       </c>
       <c r="AA21" s="9" t="n">
-        <v>55451.0029</v>
+        <v>55249.1297</v>
       </c>
       <c r="AB21" s="9" t="n">
-        <v>3500</v>
+        <v>3487.2595</v>
       </c>
       <c r="AC21" s="9" t="n">
-        <v>37543.5236</v>
+        <v>37406.8599</v>
       </c>
       <c r="AD21" s="9" t="n">
-        <v>46735.6315</v>
+        <v>46565.5073</v>
       </c>
       <c r="AE21" s="9" t="n">
         <v>0</v>
@@ -5241,7 +5272,7 @@
         <v>68571.28</v>
       </c>
       <c r="AG21" s="9" t="n">
-        <v>0</v>
+        <v>165745</v>
       </c>
       <c r="AH21" s="9" t="n">
         <v>165141.6667</v>
@@ -5330,28 +5361,28 @@
         <v>0</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>27809.9017</v>
+        <v>27463.0386</v>
       </c>
       <c r="R22" s="9" t="n">
-        <v>500</v>
+        <v>493.7641</v>
       </c>
       <c r="S22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="9" t="n">
-        <v>46705.0171</v>
+        <v>46122.4953</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>27272.5404</v>
+        <v>26932.3879</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>3000</v>
+        <v>2962.5845</v>
       </c>
       <c r="X22" s="9" t="n">
-        <v>37518.9305</v>
+        <v>37050.981</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
@@ -5360,16 +5391,16 @@
         <v>0</v>
       </c>
       <c r="AA22" s="9" t="n">
-        <v>55082.442</v>
+        <v>54395.4266</v>
       </c>
       <c r="AB22" s="9" t="n">
-        <v>3500</v>
+        <v>3456.3486</v>
       </c>
       <c r="AC22" s="9" t="n">
-        <v>37518.9305</v>
+        <v>37050.981</v>
       </c>
       <c r="AD22" s="9" t="n">
-        <v>46705.0171</v>
+        <v>46122.4953</v>
       </c>
       <c r="AE22" s="9" t="n">
         <v>0</v>
@@ -5378,7 +5409,7 @@
         <v>67238.5</v>
       </c>
       <c r="AG22" s="9" t="n">
-        <v>0</v>
+        <v>167337</v>
       </c>
       <c r="AH22" s="9" t="n">
         <v>165250</v>
@@ -5467,28 +5498,28 @@
         <v>0</v>
       </c>
       <c r="Q23" s="9" t="n">
-        <v>27886.7567</v>
+        <v>27098.8875</v>
       </c>
       <c r="R23" s="9" t="n">
-        <v>500</v>
+        <v>485.8738</v>
       </c>
       <c r="S23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="9" t="n">
-        <v>46400.3367</v>
+        <v>45089.4135</v>
       </c>
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>28111.7023</v>
+        <v>27317.4778</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>3000</v>
+        <v>2915.2427</v>
       </c>
       <c r="X23" s="9" t="n">
-        <v>37274.1756</v>
+        <v>36221.0889</v>
       </c>
       <c r="Y23" s="9" t="n">
         <v>0</v>
@@ -5497,16 +5528,16 @@
         <v>0</v>
       </c>
       <c r="AA23" s="9" t="n">
-        <v>55998.459</v>
+        <v>54416.3654</v>
       </c>
       <c r="AB23" s="9" t="n">
-        <v>3500</v>
+        <v>3401.1164</v>
       </c>
       <c r="AC23" s="9" t="n">
-        <v>37274.1756</v>
+        <v>36221.0889</v>
       </c>
       <c r="AD23" s="9" t="n">
-        <v>46400.3367</v>
+        <v>45089.4135</v>
       </c>
       <c r="AE23" s="9" t="n">
         <v>0</v>
@@ -5515,7 +5546,7 @@
         <v>63111</v>
       </c>
       <c r="AG23" s="9" t="n">
-        <v>0</v>
+        <v>171171</v>
       </c>
       <c r="AH23" s="9" t="n">
         <v>166335</v>
@@ -5604,28 +5635,28 @@
         <v>0</v>
       </c>
       <c r="Q24" s="9" t="n">
-        <v>27883.47</v>
+        <v>28593.4394</v>
       </c>
       <c r="R24" s="9" t="n">
-        <v>500</v>
+        <v>512.731</v>
       </c>
       <c r="S24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="9" t="n">
-        <v>46395.4557</v>
+        <v>47576.7775</v>
       </c>
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>28106.5359</v>
+        <v>28822.185</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>3000</v>
+        <v>3076.3861</v>
       </c>
       <c r="X24" s="9" t="n">
-        <v>36676.6803</v>
+        <v>37610.4967</v>
       </c>
       <c r="Y24" s="9" t="n">
         <v>0</v>
@@ -5634,16 +5665,16 @@
         <v>0</v>
       </c>
       <c r="AA24" s="9" t="n">
-        <v>55990.0059</v>
+        <v>57415.6244</v>
       </c>
       <c r="AB24" s="9" t="n">
-        <v>3500</v>
+        <v>3589.1171</v>
       </c>
       <c r="AC24" s="9" t="n">
-        <v>36676.6803</v>
+        <v>37610.4967</v>
       </c>
       <c r="AD24" s="9" t="n">
-        <v>46395.4557</v>
+        <v>47576.7775</v>
       </c>
       <c r="AE24" s="9" t="n">
         <v>0</v>
@@ -5652,7 +5683,7 @@
         <v>66627.205</v>
       </c>
       <c r="AG24" s="9" t="n">
-        <v>0</v>
+        <v>162222</v>
       </c>
       <c r="AH24" s="9" t="n">
         <v>166352.5</v>
@@ -5741,28 +5772,28 @@
         <v>0</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>27881.6979</v>
+        <v>28814.7367</v>
       </c>
       <c r="R25" s="9" t="n">
-        <v>500</v>
+        <v>516.7320999999999</v>
       </c>
       <c r="S25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="9" t="n">
-        <v>46391.9695</v>
+        <v>47944.4396</v>
       </c>
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>28106.0019</v>
+        <v>29046.5467</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>3000</v>
+        <v>3100.3926</v>
       </c>
       <c r="X25" s="9" t="n">
-        <v>36080.3054</v>
+        <v>37287.7039</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
@@ -5771,16 +5802,16 @@
         <v>0</v>
       </c>
       <c r="AA25" s="9" t="n">
-        <v>55987.6998</v>
+        <v>57861.2834</v>
       </c>
       <c r="AB25" s="9" t="n">
-        <v>3500</v>
+        <v>3617.1247</v>
       </c>
       <c r="AC25" s="9" t="n">
-        <v>36080.3054</v>
+        <v>37287.7039</v>
       </c>
       <c r="AD25" s="9" t="n">
-        <v>46391.9695</v>
+        <v>47944.4396</v>
       </c>
       <c r="AE25" s="9" t="n">
         <v>0</v>
@@ -5789,7 +5820,7 @@
         <v>66221.45</v>
       </c>
       <c r="AG25" s="9" t="n">
-        <v>0</v>
+        <v>160978</v>
       </c>
       <c r="AH25" s="9" t="n">
         <v>166365</v>
@@ -5878,28 +5909,28 @@
         <v>0</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>27884.3597</v>
+        <v>29183.1631</v>
       </c>
       <c r="R26" s="9" t="n">
-        <v>500</v>
+        <v>523.2891</v>
       </c>
       <c r="S26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="9" t="n">
-        <v>46398.9419</v>
+        <v>48560.1213</v>
       </c>
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>28107.4606</v>
+        <v>29416.6557</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>3000</v>
+        <v>3139.7346</v>
       </c>
       <c r="X26" s="9" t="n">
-        <v>36085.728</v>
+        <v>37766.5364</v>
       </c>
       <c r="Y26" s="9" t="n">
         <v>0</v>
@@ -5908,16 +5939,16 @@
         <v>0</v>
       </c>
       <c r="AA26" s="9" t="n">
-        <v>55991.8204</v>
+        <v>58599.8188</v>
       </c>
       <c r="AB26" s="9" t="n">
-        <v>3500</v>
+        <v>3663.0237</v>
       </c>
       <c r="AC26" s="9" t="n">
-        <v>36085.728</v>
+        <v>37766.5364</v>
       </c>
       <c r="AD26" s="9" t="n">
-        <v>46398.9419</v>
+        <v>48560.1213</v>
       </c>
       <c r="AE26" s="9" t="n">
         <v>0</v>
@@ -5926,7 +5957,7 @@
         <v>67794</v>
       </c>
       <c r="AG26" s="9" t="n">
-        <v>0</v>
+        <v>158937</v>
       </c>
       <c r="AH26" s="9" t="n">
         <v>166340</v>
@@ -6015,28 +6046,28 @@
         <v>0</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>26389.6488</v>
+        <v>28114.5895</v>
       </c>
       <c r="R27" s="9" t="n">
-        <v>500</v>
+        <v>532.6821</v>
       </c>
       <c r="S27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="9" t="n">
-        <v>46401.7315</v>
+        <v>49434.7478</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>25903.3247</v>
+        <v>27596.4772</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>3000</v>
+        <v>3196.0929</v>
       </c>
       <c r="X27" s="9" t="n">
-        <v>36087.8976</v>
+        <v>38446.7574</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
@@ -6045,16 +6076,16 @@
         <v>0</v>
       </c>
       <c r="AA27" s="9" t="n">
-        <v>52292.9736</v>
+        <v>55711.0667</v>
       </c>
       <c r="AB27" s="9" t="n">
-        <v>3500</v>
+        <v>3728.775</v>
       </c>
       <c r="AC27" s="9" t="n">
-        <v>36087.8976</v>
+        <v>38446.7574</v>
       </c>
       <c r="AD27" s="9" t="n">
-        <v>46401.7315</v>
+        <v>49434.7478</v>
       </c>
       <c r="AE27" s="9" t="n">
         <v>0</v>
@@ -6063,7 +6094,7 @@
         <v>69748.6033</v>
       </c>
       <c r="AG27" s="9" t="n">
-        <v>0</v>
+        <v>156125</v>
       </c>
       <c r="AH27" s="9" t="n">
         <v>166330</v>
@@ -6152,28 +6183,28 @@
         <v>0</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>25419.9876</v>
+        <v>27407.5821</v>
       </c>
       <c r="R28" s="9" t="n">
-        <v>500</v>
+        <v>539.0958000000001</v>
       </c>
       <c r="S28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>46394.9909</v>
+        <v>50022.6846</v>
       </c>
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>24586.4236</v>
+        <v>26508.8362</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>3000</v>
+        <v>3234.5745</v>
       </c>
       <c r="X28" s="9" t="n">
-        <v>36082.6552</v>
+        <v>38904.0119</v>
       </c>
       <c r="Y28" s="9" t="n">
         <v>0</v>
@@ -6182,16 +6213,16 @@
         <v>0</v>
       </c>
       <c r="AA28" s="9" t="n">
-        <v>50006.4112</v>
+        <v>53916.4183</v>
       </c>
       <c r="AB28" s="9" t="n">
-        <v>3500</v>
+        <v>3773.6703</v>
       </c>
       <c r="AC28" s="9" t="n">
-        <v>36082.6552</v>
+        <v>38904.0119</v>
       </c>
       <c r="AD28" s="9" t="n">
-        <v>46394.9909</v>
+        <v>50022.6846</v>
       </c>
       <c r="AE28" s="9" t="n">
         <v>0</v>
@@ -6200,7 +6231,7 @@
         <v>67958.0033</v>
       </c>
       <c r="AG28" s="9" t="n">
-        <v>0</v>
+        <v>154290</v>
       </c>
       <c r="AH28" s="9" t="n">
         <v>166354.1667</v>
@@ -6289,28 +6320,28 @@
         <v>0</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>24909.4694</v>
+        <v>27392.5438</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>500</v>
+        <v>549.842</v>
       </c>
       <c r="S29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>46395.4555</v>
+        <v>51020.3407</v>
       </c>
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>24230.1773</v>
+        <v>26645.5349</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>3000</v>
+        <v>3299.052</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>36083.0166</v>
+        <v>39679.9164</v>
       </c>
       <c r="Y29" s="9" t="n">
         <v>0</v>
@@ -6319,16 +6350,16 @@
         <v>0</v>
       </c>
       <c r="AA29" s="9" t="n">
-        <v>49139.6467</v>
+        <v>54038.0787</v>
       </c>
       <c r="AB29" s="9" t="n">
-        <v>3500</v>
+        <v>3848.8941</v>
       </c>
       <c r="AC29" s="9" t="n">
-        <v>36083.0166</v>
+        <v>39679.9164</v>
       </c>
       <c r="AD29" s="9" t="n">
-        <v>46395.4555</v>
+        <v>51020.3407</v>
       </c>
       <c r="AE29" s="9" t="n">
         <v>0</v>
@@ -6337,7 +6368,7 @@
         <v>67803.50999999999</v>
       </c>
       <c r="AG29" s="9" t="n">
-        <v>0</v>
+        <v>151273</v>
       </c>
       <c r="AH29" s="9" t="n">
         <v>166352.5</v>
@@ -6426,28 +6457,28 @@
         <v>0</v>
       </c>
       <c r="Q30" s="9" t="n">
-        <v>25154.0781</v>
+        <v>27591.8635</v>
       </c>
       <c r="R30" s="9" t="n">
-        <v>500</v>
+        <v>548.457</v>
       </c>
       <c r="S30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="9" t="n">
-        <v>46396.9895</v>
+        <v>50893.5048</v>
       </c>
       <c r="U30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>24201.8182</v>
+        <v>26547.3129</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>3000</v>
+        <v>3290.7418</v>
       </c>
       <c r="X30" s="9" t="n">
-        <v>36084.2095</v>
+        <v>39581.2727</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
@@ -6456,16 +6487,16 @@
         <v>0</v>
       </c>
       <c r="AA30" s="9" t="n">
-        <v>49355.8963</v>
+        <v>54139.1764</v>
       </c>
       <c r="AB30" s="9" t="n">
-        <v>3500</v>
+        <v>3839.1988</v>
       </c>
       <c r="AC30" s="9" t="n">
-        <v>36084.2095</v>
+        <v>39581.2727</v>
       </c>
       <c r="AD30" s="9" t="n">
-        <v>46396.9895</v>
+        <v>50893.5048</v>
       </c>
       <c r="AE30" s="9" t="n">
         <v>0</v>
@@ -6474,7 +6505,7 @@
         <v>68151.90399999999</v>
       </c>
       <c r="AG30" s="9" t="n">
-        <v>0</v>
+        <v>151650</v>
       </c>
       <c r="AH30" s="9" t="n">
         <v>166347</v>
@@ -6563,28 +6594,28 @@
         <v>0</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>24864.9392</v>
+        <v>28013.9486</v>
       </c>
       <c r="R31" s="9" t="n">
-        <v>500</v>
+        <v>563.3225</v>
       </c>
       <c r="S31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="9" t="n">
-        <v>46395.4556</v>
+        <v>52271.2034</v>
       </c>
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>24188.8454</v>
+        <v>27252.24</v>
       </c>
       <c r="W31" s="9" t="n">
-        <v>3000</v>
+        <v>3379.9347</v>
       </c>
       <c r="X31" s="9" t="n">
-        <v>36083.0166</v>
+        <v>40652.7466</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -6593,16 +6624,16 @@
         <v>0</v>
       </c>
       <c r="AA31" s="9" t="n">
-        <v>49053.7846</v>
+        <v>55266.1886</v>
       </c>
       <c r="AB31" s="9" t="n">
-        <v>3500</v>
+        <v>3943.2572</v>
       </c>
       <c r="AC31" s="9" t="n">
-        <v>36083.0166</v>
+        <v>40652.7466</v>
       </c>
       <c r="AD31" s="9" t="n">
-        <v>46395.4556</v>
+        <v>52271.2034</v>
       </c>
       <c r="AE31" s="9" t="n">
         <v>0</v>
@@ -6611,7 +6642,7 @@
         <v>70201.5</v>
       </c>
       <c r="AG31" s="9" t="n">
-        <v>0</v>
+        <v>147653</v>
       </c>
       <c r="AH31" s="9" t="n">
         <v>166352.5</v>
@@ -6700,28 +6731,28 @@
         <v>0</v>
       </c>
       <c r="Q32" s="9" t="n">
-        <v>24711.8104</v>
+        <v>28340.652</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>500</v>
+        <v>573.4233</v>
       </c>
       <c r="S32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="9" t="n">
-        <v>46391.9695</v>
+        <v>53204.4698</v>
       </c>
       <c r="U32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>24341.058</v>
+        <v>27915.4574</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>3000</v>
+        <v>3440.5396</v>
       </c>
       <c r="X32" s="9" t="n">
-        <v>36080.3054</v>
+        <v>41378.5734</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
@@ -6730,16 +6761,16 @@
         <v>0</v>
       </c>
       <c r="AA32" s="9" t="n">
-        <v>49052.8684</v>
+        <v>56256.1095</v>
       </c>
       <c r="AB32" s="9" t="n">
-        <v>3500</v>
+        <v>4013.9629</v>
       </c>
       <c r="AC32" s="9" t="n">
-        <v>36080.3054</v>
+        <v>41378.5734</v>
       </c>
       <c r="AD32" s="9" t="n">
-        <v>46391.9695</v>
+        <v>53204.4698</v>
       </c>
       <c r="AE32" s="9" t="n">
         <v>0</v>
@@ -6748,7 +6779,7 @@
         <v>69692.73669999999</v>
       </c>
       <c r="AG32" s="9" t="n">
-        <v>0</v>
+        <v>145063</v>
       </c>
       <c r="AH32" s="9" t="n">
         <v>166365</v>
@@ -6837,28 +6868,28 @@
         <v>0</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>28695.8204</v>
+        <v>29156.8104</v>
       </c>
       <c r="R33" s="9" t="n">
-        <v>571.7852</v>
+        <v>581.1211</v>
       </c>
       <c r="S33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="9" t="n">
-        <v>53058.8641</v>
+        <v>53925.1911</v>
       </c>
       <c r="U33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>27782.8451</v>
+        <v>28237.7847</v>
       </c>
       <c r="W33" s="9" t="n">
-        <v>3430.7114</v>
+        <v>3486.7268</v>
       </c>
       <c r="X33" s="9" t="n">
-        <v>41265.3319</v>
+        <v>41939.0982</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
@@ -6867,16 +6898,16 @@
         <v>0</v>
       </c>
       <c r="AA33" s="9" t="n">
-        <v>56478.6655</v>
+        <v>57394.5951</v>
       </c>
       <c r="AB33" s="9" t="n">
-        <v>4002.4966</v>
+        <v>4067.848</v>
       </c>
       <c r="AC33" s="9" t="n">
-        <v>41265.3319</v>
+        <v>41939.0982</v>
       </c>
       <c r="AD33" s="9" t="n">
-        <v>53058.8641</v>
+        <v>53925.1911</v>
       </c>
       <c r="AE33" s="9" t="n">
         <v>0</v>
@@ -6885,7 +6916,7 @@
         <v>70416.4011</v>
       </c>
       <c r="AG33" s="9" t="n">
-        <v>143213.875</v>
+        <v>143124.8889</v>
       </c>
       <c r="AH33" s="9" t="n">
         <v>166345</v>
@@ -7477,7 +7508,7 @@
         <v>46098</v>
       </c>
       <c r="B38" s="9" t="n">
-        <v>3808290728</v>
+        <v>4043290728</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>83180000</v>
@@ -7507,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>7744290728</v>
+        <v>7979290728</v>
       </c>
       <c r="M38" s="9" t="n">
         <v>582260000</v>
@@ -7522,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>26155.4836</v>
+        <v>27769.4725</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>571.2834</v>
@@ -7552,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="AA38" s="9" t="n">
-        <v>53188.0793</v>
+        <v>54802.0682</v>
       </c>
       <c r="AB38" s="9" t="n">
         <v>3998.9835</v>
@@ -7567,7 +7598,7 @@
         <v>0</v>
       </c>
       <c r="AF38" s="9" t="n">
-        <v>74375</v>
+        <v>74350</v>
       </c>
       <c r="AG38" s="9" t="n">
         <v>145602</v>
@@ -7588,10 +7619,10 @@
         <v>45644074</v>
       </c>
       <c r="AM38" s="9" t="n">
-        <v>15000000</v>
+        <v>30000000</v>
       </c>
       <c r="AN38" s="9" t="n">
-        <v>35000000</v>
+        <v>70000000</v>
       </c>
       <c r="AO38" s="9" t="n">
         <v>26000000</v>
@@ -7606,7 +7637,7 @@
         <v>191950</v>
       </c>
       <c r="AS38" s="9" t="n">
-        <v>5025</v>
+        <v>5023</v>
       </c>
     </row>
     <row r="39">
@@ -8984,10 +9015,10 @@
         <v>46111</v>
       </c>
       <c r="B49" s="9" t="n">
-        <v>4277114373</v>
+        <v>4269906860.4</v>
       </c>
       <c r="C49" s="9" t="n">
-        <v>77997500</v>
+        <v>77998000</v>
       </c>
       <c r="D49" s="9" t="n">
         <v>0</v>
@@ -8999,10 +9030,10 @@
         <v>0</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>4128166666.6667</v>
+        <v>4123500000</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>467985000</v>
+        <v>467988000</v>
       </c>
       <c r="I49" s="9" t="n">
         <v>6002500000</v>
@@ -9014,10 +9045,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>8405281039.6667</v>
+        <v>8393406860.4</v>
       </c>
       <c r="M49" s="9" t="n">
-        <v>545982500</v>
+        <v>545986000</v>
       </c>
       <c r="N49" s="9" t="n">
         <v>6002500000</v>
@@ -9029,28 +9060,28 @@
         <v>0</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>27213.8231</v>
+        <v>27200.3205</v>
       </c>
       <c r="R49" s="9" t="n">
-        <v>496.2837</v>
+        <v>496.8745</v>
       </c>
       <c r="S49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="9" t="n">
-        <v>49108.2005</v>
+        <v>49166.338</v>
       </c>
       <c r="U49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>26266.3312</v>
+        <v>26267.8248</v>
       </c>
       <c r="W49" s="9" t="n">
-        <v>2977.7025</v>
+        <v>2981.2468</v>
       </c>
       <c r="X49" s="9" t="n">
-        <v>38192.7927</v>
+        <v>38238.0078</v>
       </c>
       <c r="Y49" s="9" t="n">
         <v>0</v>
@@ -9059,40 +9090,40 @@
         <v>0</v>
       </c>
       <c r="AA49" s="9" t="n">
-        <v>53480.1542</v>
+        <v>53468.1452</v>
       </c>
       <c r="AB49" s="9" t="n">
-        <v>3473.9862</v>
+        <v>3478.1213</v>
       </c>
       <c r="AC49" s="9" t="n">
-        <v>38192.7927</v>
+        <v>38238.0078</v>
       </c>
       <c r="AD49" s="9" t="n">
-        <v>49108.2005</v>
+        <v>49166.338</v>
       </c>
       <c r="AE49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF49" s="9" t="n">
-        <v>66971.81</v>
+        <v>66931.576</v>
       </c>
       <c r="AG49" s="9" t="n">
-        <v>157166</v>
+        <v>156979.4</v>
       </c>
       <c r="AH49" s="9" t="n">
-        <v>155995</v>
+        <v>155996</v>
       </c>
       <c r="AI49" s="9" t="n">
-        <v>184000000</v>
+        <v>183800000</v>
       </c>
       <c r="AJ49" s="9" t="n">
-        <v>96416666.66670001</v>
+        <v>96300000</v>
       </c>
       <c r="AK49" s="9" t="n">
-        <v>55916666.6667</v>
+        <v>55800000</v>
       </c>
       <c r="AL49" s="9" t="n">
-        <v>48614561.5</v>
+        <v>48513130.2</v>
       </c>
       <c r="AM49" s="9" t="n">
         <v>30000000</v>
@@ -9101,10 +9132,10 @@
         <v>70000000</v>
       </c>
       <c r="AO49" s="9" t="n">
-        <v>27666666.6667</v>
+        <v>27500000</v>
       </c>
       <c r="AP49" s="9" t="n">
-        <v>17987183.3333</v>
+        <v>17955640</v>
       </c>
       <c r="AQ49" s="9" t="n">
         <v>2401</v>
@@ -9113,7 +9144,7 @@
         <v>182520</v>
       </c>
       <c r="AS49" s="9" t="n">
-        <v>4540.3333</v>
+        <v>4535.4</v>
       </c>
     </row>
     <row r="50">
@@ -9669,10 +9700,10 @@
         <v>46116</v>
       </c>
       <c r="B54" s="9" t="n">
-        <v>4281417051</v>
+        <v>4284950619.3333</v>
       </c>
       <c r="C54" s="9" t="n">
-        <v>77460000</v>
+        <v>77465000</v>
       </c>
       <c r="D54" s="9" t="n">
         <v>0</v>
@@ -9684,10 +9715,10 @@
         <v>0</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>4133375000</v>
+        <v>4137166666.6667</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>464760000</v>
+        <v>464790000</v>
       </c>
       <c r="I54" s="9" t="n">
         <v>6002500000</v>
@@ -9699,10 +9730,10 @@
         <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>8414792051</v>
+        <v>8422117286</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>542220000</v>
+        <v>542255000</v>
       </c>
       <c r="N54" s="9" t="n">
         <v>6002500000</v>
@@ -9714,28 +9745,28 @@
         <v>0</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>27146.9023</v>
+        <v>27146.1879</v>
       </c>
       <c r="R54" s="9" t="n">
-        <v>491.1482</v>
+        <v>490.7615</v>
       </c>
       <c r="S54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="9" t="n">
-        <v>48937.4398</v>
+        <v>48895.7995</v>
       </c>
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>26208.2651</v>
+        <v>26210.0073</v>
       </c>
       <c r="W54" s="9" t="n">
-        <v>2946.8892</v>
+        <v>2944.5693</v>
       </c>
       <c r="X54" s="9" t="n">
-        <v>38059.9874</v>
+        <v>38027.6025</v>
       </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
@@ -9744,40 +9775,40 @@
         <v>0</v>
       </c>
       <c r="AA54" s="9" t="n">
-        <v>53355.1674</v>
+        <v>53356.1952</v>
       </c>
       <c r="AB54" s="9" t="n">
-        <v>3438.0374</v>
+        <v>3435.3308</v>
       </c>
       <c r="AC54" s="9" t="n">
-        <v>38059.9874</v>
+        <v>38027.6025</v>
       </c>
       <c r="AD54" s="9" t="n">
-        <v>48937.4398</v>
+        <v>48895.7995</v>
       </c>
       <c r="AE54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF54" s="9" t="n">
-        <v>67071.75</v>
+        <v>67058</v>
       </c>
       <c r="AG54" s="9" t="n">
-        <v>157713.5</v>
+        <v>157848</v>
       </c>
       <c r="AH54" s="9" t="n">
-        <v>154920</v>
+        <v>154930</v>
       </c>
       <c r="AI54" s="9" t="n">
-        <v>184000000</v>
+        <v>184166666.6667</v>
       </c>
       <c r="AJ54" s="9" t="n">
-        <v>97625000</v>
+        <v>97666666.66670001</v>
       </c>
       <c r="AK54" s="9" t="n">
-        <v>57250000</v>
+        <v>57333333.3333</v>
       </c>
       <c r="AL54" s="9" t="n">
-        <v>49773775.5</v>
+        <v>49846226.3333</v>
       </c>
       <c r="AM54" s="9" t="n">
         <v>30000000</v>
@@ -9786,10 +9817,10 @@
         <v>70000000</v>
       </c>
       <c r="AO54" s="9" t="n">
-        <v>28750000</v>
+        <v>28833333.3333</v>
       </c>
       <c r="AP54" s="9" t="n">
-        <v>17908300</v>
+        <v>17921766.6667</v>
       </c>
       <c r="AQ54" s="9" t="n">
         <v>2401</v>
@@ -9943,10 +9974,10 @@
         <v>46118</v>
       </c>
       <c r="B56" s="9" t="n">
-        <v>4310630089.3333</v>
+        <v>4318231756</v>
       </c>
       <c r="C56" s="9" t="n">
-        <v>77938333.33329999</v>
+        <v>78080000</v>
       </c>
       <c r="D56" s="9" t="n">
         <v>0</v>
@@ -9958,10 +9989,10 @@
         <v>0</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>4148300000</v>
+        <v>4153100000</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>467630000</v>
+        <v>468480000</v>
       </c>
       <c r="I56" s="9" t="n">
         <v>6002500000</v>
@@ -9973,10 +10004,10 @@
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>8458930089.3333</v>
+        <v>8471331756</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>545568333.3333</v>
+        <v>546560000</v>
       </c>
       <c r="N56" s="9" t="n">
         <v>6002500000</v>
@@ -9988,28 +10019,28 @@
         <v>0</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>27336.2798</v>
+        <v>27394.845</v>
       </c>
       <c r="R56" s="9" t="n">
-        <v>494.2536</v>
+        <v>495.3393</v>
       </c>
       <c r="S56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T56" s="9" t="n">
-        <v>48944.1867</v>
+        <v>48962.6684</v>
       </c>
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>26306.7996</v>
+        <v>26347.1957</v>
       </c>
       <c r="W56" s="9" t="n">
-        <v>2965.5216</v>
+        <v>2972.0358</v>
       </c>
       <c r="X56" s="9" t="n">
-        <v>38065.2346</v>
+        <v>38079.6083</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -10018,34 +10049,34 @@
         <v>0</v>
       </c>
       <c r="AA56" s="9" t="n">
-        <v>53643.0794</v>
+        <v>53742.0407</v>
       </c>
       <c r="AB56" s="9" t="n">
-        <v>3459.7752</v>
+        <v>3467.3751</v>
       </c>
       <c r="AC56" s="9" t="n">
-        <v>38065.2346</v>
+        <v>38079.6083</v>
       </c>
       <c r="AD56" s="9" t="n">
-        <v>48944.1867</v>
+        <v>48962.6684</v>
       </c>
       <c r="AE56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF56" s="9" t="n">
-        <v>67796</v>
+        <v>68232</v>
       </c>
       <c r="AG56" s="9" t="n">
-        <v>157690</v>
+        <v>157630.5</v>
       </c>
       <c r="AH56" s="9" t="n">
-        <v>155876.6667</v>
+        <v>156160</v>
       </c>
       <c r="AI56" s="9" t="n">
-        <v>184633333.3333</v>
+        <v>184850000</v>
       </c>
       <c r="AJ56" s="9" t="n">
-        <v>98500000</v>
+        <v>98750000</v>
       </c>
       <c r="AK56" s="9" t="n">
         <v>57500000</v>
@@ -10060,19 +10091,19 @@
         <v>70000000</v>
       </c>
       <c r="AO56" s="9" t="n">
-        <v>28700000</v>
+        <v>28800000</v>
       </c>
       <c r="AP56" s="9" t="n">
-        <v>18067966.6667</v>
+        <v>18110300</v>
       </c>
       <c r="AQ56" s="9" t="n">
         <v>2401</v>
       </c>
       <c r="AR56" s="9" t="n">
-        <v>180956.6667</v>
+        <v>181035</v>
       </c>
       <c r="AS56" s="9" t="n">
-        <v>4666.6667</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="57">
@@ -10354,10 +10385,10 @@
         <v>46121</v>
       </c>
       <c r="B59" s="9" t="n">
-        <v>4312697671.2</v>
+        <v>4308897605</v>
       </c>
       <c r="C59" s="9" t="n">
-        <v>76407000</v>
+        <v>76322500</v>
       </c>
       <c r="D59" s="9" t="n">
         <v>0</v>
@@ -10369,10 +10400,10 @@
         <v>0</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>4178300000</v>
+        <v>4176500000</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>458442000</v>
+        <v>457935000</v>
       </c>
       <c r="I59" s="9" t="n">
         <v>6002500000</v>
@@ -10384,10 +10415,10 @@
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>8490997671.2</v>
+        <v>8485397605</v>
       </c>
       <c r="M59" s="9" t="n">
-        <v>534849000</v>
+        <v>534257500</v>
       </c>
       <c r="N59" s="9" t="n">
         <v>6002500000</v>
@@ -10399,28 +10430,28 @@
         <v>0</v>
       </c>
       <c r="Q59" s="9" t="n">
-        <v>27574.7848</v>
+        <v>27557.1141</v>
       </c>
       <c r="R59" s="9" t="n">
-        <v>488.5346</v>
+        <v>488.1116</v>
       </c>
       <c r="S59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T59" s="9" t="n">
-        <v>49347.9071</v>
+        <v>49359.7481</v>
       </c>
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>26715.5099</v>
+        <v>26710.4206</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>2931.2077</v>
+        <v>2928.6695</v>
       </c>
       <c r="X59" s="9" t="n">
-        <v>38379.219</v>
+        <v>38388.4281</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -10429,40 +10460,40 @@
         <v>0</v>
       </c>
       <c r="AA59" s="9" t="n">
-        <v>54290.2947</v>
+        <v>54267.5347</v>
       </c>
       <c r="AB59" s="9" t="n">
-        <v>3419.7423</v>
+        <v>3416.7811</v>
       </c>
       <c r="AC59" s="9" t="n">
-        <v>38379.219</v>
+        <v>38388.4281</v>
       </c>
       <c r="AD59" s="9" t="n">
-        <v>49347.9071</v>
+        <v>49359.7481</v>
       </c>
       <c r="AE59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF59" s="9" t="n">
-        <v>71024.8</v>
+        <v>71080.5</v>
       </c>
       <c r="AG59" s="9" t="n">
-        <v>156400</v>
+        <v>156362.5</v>
       </c>
       <c r="AH59" s="9" t="n">
-        <v>152814</v>
+        <v>152645</v>
       </c>
       <c r="AI59" s="9" t="n">
-        <v>186200000</v>
+        <v>186125000</v>
       </c>
       <c r="AJ59" s="9" t="n">
-        <v>99200000</v>
+        <v>99125000</v>
       </c>
       <c r="AK59" s="9" t="n">
-        <v>56300000</v>
+        <v>56250000</v>
       </c>
       <c r="AL59" s="9" t="n">
-        <v>48947835.6</v>
+        <v>48904365</v>
       </c>
       <c r="AM59" s="9" t="n">
         <v>30000000</v>
@@ -10474,16 +10505,16 @@
         <v>28000000</v>
       </c>
       <c r="AP59" s="9" t="n">
-        <v>18158800</v>
+        <v>18139175</v>
       </c>
       <c r="AQ59" s="9" t="n">
         <v>2401</v>
       </c>
       <c r="AR59" s="9" t="n">
-        <v>180868</v>
+        <v>181012.5</v>
       </c>
       <c r="AS59" s="9" t="n">
-        <v>4734.2</v>
+        <v>4737.25</v>
       </c>
     </row>
     <row r="60">
@@ -16656,7 +16687,7 @@
         <v>46199</v>
       </c>
       <c r="B105" s="9" t="n">
-        <v>3826890240</v>
+        <v>3851202740</v>
       </c>
       <c r="C105" s="9" t="n">
         <v>80000000</v>
@@ -16686,7 +16717,7 @@
         <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>7483950240</v>
+        <v>7508262740</v>
       </c>
       <c r="M105" s="9" t="n">
         <v>560000000</v>
@@ -16701,28 +16732,28 @@
         <v>0</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>23657.647</v>
+        <v>23375.5717</v>
       </c>
       <c r="R105" s="9" t="n">
-        <v>494.6176</v>
+        <v>485.647</v>
       </c>
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T105" s="9" t="n">
-        <v>47718.2339</v>
+        <v>46852.7905</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>22610.5785</v>
+        <v>22200.5009</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>2967.7057</v>
+        <v>2913.8818</v>
       </c>
       <c r="X105" s="9" t="n">
-        <v>48209.7602</v>
+        <v>47335.4021</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -16731,16 +16762,16 @@
         <v>0</v>
       </c>
       <c r="AA105" s="9" t="n">
-        <v>46268.2254</v>
+        <v>45576.0726</v>
       </c>
       <c r="AB105" s="9" t="n">
-        <v>3462.3233</v>
+        <v>3399.5287</v>
       </c>
       <c r="AC105" s="9" t="n">
-        <v>48209.7602</v>
+        <v>47335.4021</v>
       </c>
       <c r="AD105" s="9" t="n">
-        <v>47718.2339</v>
+        <v>46852.7905</v>
       </c>
       <c r="AE105" s="9" t="n">
         <v>0</v>
@@ -16767,10 +16798,10 @@
         <v>42992370</v>
       </c>
       <c r="AM105" s="9" t="n">
-        <v>26925000</v>
+        <v>28633333.3333</v>
       </c>
       <c r="AN105" s="9" t="n">
-        <v>63707500</v>
+        <v>67203333.33329999</v>
       </c>
       <c r="AO105" s="9" t="n">
         <v>25500000</v>
@@ -16793,10 +16824,10 @@
         <v>46201</v>
       </c>
       <c r="B106" s="9" t="n">
-        <v>3964329720</v>
+        <v>3977806885.4286</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>85312187.5</v>
+        <v>85463928.5714</v>
       </c>
       <c r="D106" s="9" t="n">
         <v>0</v>
@@ -16808,13 +16839,13 @@
         <v>0</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>3819988125</v>
+        <v>3833620000</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>511873125</v>
+        <v>512783571.4286</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>7718750000</v>
+        <v>7721428571.4286</v>
       </c>
       <c r="J106" s="9" t="n">
         <v>0</v>
@@ -16823,13 +16854,13 @@
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>7784317845</v>
+        <v>7811426885.4286</v>
       </c>
       <c r="M106" s="9" t="n">
-        <v>597185312.5</v>
+        <v>598247500</v>
       </c>
       <c r="N106" s="9" t="n">
-        <v>7718750000</v>
+        <v>7721428571.4286</v>
       </c>
       <c r="O106" s="9" t="n">
         <v>7718000000</v>
@@ -16838,28 +16869,28 @@
         <v>0</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>23257.7393</v>
+        <v>23299.231</v>
       </c>
       <c r="R106" s="9" t="n">
-        <v>500.5435</v>
+        <v>500.6212</v>
       </c>
       <c r="S106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T106" s="9" t="n">
-        <v>45287.5748</v>
+        <v>45213.7778</v>
       </c>
       <c r="U106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>22410.7236</v>
+        <v>22454.5065</v>
       </c>
       <c r="W106" s="9" t="n">
-        <v>3003.2611</v>
+        <v>3003.727</v>
       </c>
       <c r="X106" s="9" t="n">
-        <v>45293.5618</v>
+        <v>45235.8807</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -16868,16 +16899,16 @@
         <v>0</v>
       </c>
       <c r="AA106" s="9" t="n">
-        <v>45668.4628</v>
+        <v>45753.7375</v>
       </c>
       <c r="AB106" s="9" t="n">
-        <v>3503.8046</v>
+        <v>3504.3482</v>
       </c>
       <c r="AC106" s="9" t="n">
-        <v>45293.5618</v>
+        <v>45235.8807</v>
       </c>
       <c r="AD106" s="9" t="n">
-        <v>45287.5748</v>
+        <v>45213.7778</v>
       </c>
       <c r="AE106" s="9" t="n">
         <v>0</v>
@@ -16889,19 +16920,19 @@
         <v>171452</v>
       </c>
       <c r="AH106" s="9" t="n">
-        <v>170624.375</v>
+        <v>170927.8571</v>
       </c>
       <c r="AI106" s="9" t="n">
-        <v>170250625</v>
+        <v>170857142.8571</v>
       </c>
       <c r="AJ106" s="9" t="n">
-        <v>88620000</v>
+        <v>88835714.28569999</v>
       </c>
       <c r="AK106" s="9" t="n">
-        <v>52035000</v>
+        <v>52261428.5714</v>
       </c>
       <c r="AL106" s="9" t="n">
-        <v>45239797.5</v>
+        <v>45436657</v>
       </c>
       <c r="AM106" s="9" t="n">
         <v>25900000</v>
@@ -16910,13 +16941,13 @@
         <v>61610000</v>
       </c>
       <c r="AO106" s="9" t="n">
-        <v>26812500</v>
+        <v>26857142.8571</v>
       </c>
       <c r="AP106" s="9" t="n">
-        <v>16778300</v>
+        <v>16841857.1429</v>
       </c>
       <c r="AQ106" s="9" t="n">
-        <v>3087.5</v>
+        <v>3088.5714</v>
       </c>
       <c r="AR106" s="9" t="n">
         <v>196190</v>
@@ -17067,10 +17098,10 @@
         <v>46208</v>
       </c>
       <c r="B108" s="9" t="n">
-        <v>4122950413.1429</v>
+        <v>4128003471.3333</v>
       </c>
       <c r="C108" s="9" t="n">
-        <v>87343571.4286</v>
+        <v>87411666.66670001</v>
       </c>
       <c r="D108" s="9" t="n">
         <v>0</v>
@@ -17082,10 +17113,10 @@
         <v>0</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>3988238571.4286</v>
+        <v>3989585000</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>524061428.5714</v>
+        <v>524470000</v>
       </c>
       <c r="I108" s="9" t="n">
         <v>7650000000</v>
@@ -17097,10 +17128,10 @@
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>8111188984.5714</v>
+        <v>8117588471.3333</v>
       </c>
       <c r="M108" s="9" t="n">
-        <v>611405000</v>
+        <v>611881666.6667</v>
       </c>
       <c r="N108" s="9" t="n">
         <v>7650000000</v>
@@ -17112,28 +17143,28 @@
         <v>0</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>23680.6792</v>
+        <v>23704.4217</v>
       </c>
       <c r="R108" s="9" t="n">
-        <v>501.6694</v>
+        <v>501.9482</v>
       </c>
       <c r="S108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="T108" s="9" t="n">
-        <v>44329.4707</v>
+        <v>44319.6038</v>
       </c>
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>22906.9744</v>
+        <v>22909.6093</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>3010.0163</v>
+        <v>3011.689</v>
       </c>
       <c r="X108" s="9" t="n">
-        <v>43938.9027</v>
+        <v>43929.1227</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -17142,40 +17173,40 @@
         <v>0</v>
       </c>
       <c r="AA108" s="9" t="n">
-        <v>46587.6536</v>
+        <v>46614.031</v>
       </c>
       <c r="AB108" s="9" t="n">
-        <v>3511.6857</v>
+        <v>3513.6372</v>
       </c>
       <c r="AC108" s="9" t="n">
-        <v>43938.9027</v>
+        <v>43929.1227</v>
       </c>
       <c r="AD108" s="9" t="n">
-        <v>44329.4707</v>
+        <v>44319.6038</v>
       </c>
       <c r="AE108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AF108" s="9" t="n">
-        <v>62955</v>
+        <v>62884.6667</v>
       </c>
       <c r="AG108" s="9" t="n">
-        <v>174105.5714</v>
+        <v>174144.6667</v>
       </c>
       <c r="AH108" s="9" t="n">
-        <v>174687.1429</v>
+        <v>174823.3333</v>
       </c>
       <c r="AI108" s="9" t="n">
-        <v>177852857.1429</v>
+        <v>177907222.2222</v>
       </c>
       <c r="AJ108" s="9" t="n">
-        <v>92794285.71430001</v>
+        <v>92840000</v>
       </c>
       <c r="AK108" s="9" t="n">
-        <v>53511428.5714</v>
+        <v>53564444.4444</v>
       </c>
       <c r="AL108" s="9" t="n">
-        <v>46523420.8571</v>
+        <v>46569513.4444</v>
       </c>
       <c r="AM108" s="9" t="n">
         <v>25900000</v>
@@ -17184,19 +17215,978 @@
         <v>61610000</v>
       </c>
       <c r="AO108" s="9" t="n">
-        <v>27071428.5714</v>
+        <v>27166666.6667</v>
       </c>
       <c r="AP108" s="9" t="n">
-        <v>17600142.8571</v>
+        <v>17625000</v>
       </c>
       <c r="AQ108" s="9" t="n">
         <v>3060</v>
       </c>
       <c r="AR108" s="9" t="n">
-        <v>200561.4286</v>
+        <v>200550</v>
       </c>
       <c r="AS108" s="9" t="n">
-        <v>4152.2857</v>
+        <v>4157.3333</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B109" s="9" t="n">
+        <v>4149150880</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>87883333.33329999</v>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="9" t="n">
+        <v>4011035000</v>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>527300000</v>
+      </c>
+      <c r="I109" s="9" t="n">
+        <v>7650000000</v>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="9" t="n">
+        <v>8160185880</v>
+      </c>
+      <c r="M109" s="9" t="n">
+        <v>615183333.3333</v>
+      </c>
+      <c r="N109" s="9" t="n">
+        <v>7650000000</v>
+      </c>
+      <c r="O109" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="P109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="9" t="n">
+        <v>23704.8266</v>
+      </c>
+      <c r="R109" s="9" t="n">
+        <v>502.0929</v>
+      </c>
+      <c r="S109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" s="9" t="n">
+        <v>44094.2911</v>
+      </c>
+      <c r="U109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="9" t="n">
+        <v>22915.7443</v>
+      </c>
+      <c r="W109" s="9" t="n">
+        <v>3012.5575</v>
+      </c>
+      <c r="X109" s="9" t="n">
+        <v>43705.7951</v>
+      </c>
+      <c r="Y109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="9" t="n">
+        <v>46620.5709</v>
+      </c>
+      <c r="AB109" s="9" t="n">
+        <v>3514.6504</v>
+      </c>
+      <c r="AC109" s="9" t="n">
+        <v>43705.7951</v>
+      </c>
+      <c r="AD109" s="9" t="n">
+        <v>44094.2911</v>
+      </c>
+      <c r="AE109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" s="9" t="n">
+        <v>62604.3333</v>
+      </c>
+      <c r="AG109" s="9" t="n">
+        <v>175034</v>
+      </c>
+      <c r="AH109" s="9" t="n">
+        <v>175766.6667</v>
+      </c>
+      <c r="AI109" s="9" t="n">
+        <v>178835000</v>
+      </c>
+      <c r="AJ109" s="9" t="n">
+        <v>93500000</v>
+      </c>
+      <c r="AK109" s="9" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="AL109" s="9" t="n">
+        <v>46948190</v>
+      </c>
+      <c r="AM109" s="9" t="n">
+        <v>25900000</v>
+      </c>
+      <c r="AN109" s="9" t="n">
+        <v>61610000</v>
+      </c>
+      <c r="AO109" s="9" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="AP109" s="9" t="n">
+        <v>17701633.3333</v>
+      </c>
+      <c r="AQ109" s="9" t="n">
+        <v>3060</v>
+      </c>
+      <c r="AR109" s="9" t="n">
+        <v>200680</v>
+      </c>
+      <c r="AS109" s="9" t="n">
+        <v>4148.6667</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B110" s="9" t="n">
+        <v>4147374410</v>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>88342500</v>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="9" t="n">
+        <v>4012475000</v>
+      </c>
+      <c r="H110" s="9" t="n">
+        <v>530055000</v>
+      </c>
+      <c r="I110" s="9" t="n">
+        <v>7650000000</v>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="9" t="n">
+        <v>8159849410</v>
+      </c>
+      <c r="M110" s="9" t="n">
+        <v>618397500</v>
+      </c>
+      <c r="N110" s="9" t="n">
+        <v>7650000000</v>
+      </c>
+      <c r="O110" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="P110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="9" t="n">
+        <v>23484.9025</v>
+      </c>
+      <c r="R110" s="9" t="n">
+        <v>500.2478</v>
+      </c>
+      <c r="S110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" s="9" t="n">
+        <v>43703.91</v>
+      </c>
+      <c r="U110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="9" t="n">
+        <v>22721.0218</v>
+      </c>
+      <c r="W110" s="9" t="n">
+        <v>3001.4869</v>
+      </c>
+      <c r="X110" s="9" t="n">
+        <v>43318.8535</v>
+      </c>
+      <c r="Y110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" s="9" t="n">
+        <v>46205.9243</v>
+      </c>
+      <c r="AB110" s="9" t="n">
+        <v>3501.7347</v>
+      </c>
+      <c r="AC110" s="9" t="n">
+        <v>43318.8535</v>
+      </c>
+      <c r="AD110" s="9" t="n">
+        <v>43703.91</v>
+      </c>
+      <c r="AE110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF110" s="9" t="n">
+        <v>63904.5</v>
+      </c>
+      <c r="AG110" s="9" t="n">
+        <v>176599.5</v>
+      </c>
+      <c r="AH110" s="9" t="n">
+        <v>176685</v>
+      </c>
+      <c r="AI110" s="9" t="n">
+        <v>178995000</v>
+      </c>
+      <c r="AJ110" s="9" t="n">
+        <v>92930000</v>
+      </c>
+      <c r="AK110" s="9" t="n">
+        <v>53550000</v>
+      </c>
+      <c r="AL110" s="9" t="n">
+        <v>46556955</v>
+      </c>
+      <c r="AM110" s="9" t="n">
+        <v>25900000</v>
+      </c>
+      <c r="AN110" s="9" t="n">
+        <v>61610000</v>
+      </c>
+      <c r="AO110" s="9" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="AP110" s="9" t="n">
+        <v>17740700</v>
+      </c>
+      <c r="AQ110" s="9" t="n">
+        <v>3060</v>
+      </c>
+      <c r="AR110" s="9" t="n">
+        <v>201800</v>
+      </c>
+      <c r="AS110" s="9" t="n">
+        <v>4126</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B111" s="9" t="n">
+        <v>4171994380</v>
+      </c>
+      <c r="C111" s="9" t="n">
+        <v>90250000</v>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="9" t="n">
+        <v>4036690000</v>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>541500000</v>
+      </c>
+      <c r="I111" s="9" t="n">
+        <v>7050000000</v>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="9" t="n">
+        <v>8208684380</v>
+      </c>
+      <c r="M111" s="9" t="n">
+        <v>631750000</v>
+      </c>
+      <c r="N111" s="9" t="n">
+        <v>7050000000</v>
+      </c>
+      <c r="O111" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="P111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="9" t="n">
+        <v>23272.7771</v>
+      </c>
+      <c r="R111" s="9" t="n">
+        <v>503.4446</v>
+      </c>
+      <c r="S111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" s="9" t="n">
+        <v>43053.5799</v>
+      </c>
+      <c r="U111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9" t="n">
+        <v>22518.0041</v>
+      </c>
+      <c r="W111" s="9" t="n">
+        <v>3020.6677</v>
+      </c>
+      <c r="X111" s="9" t="n">
+        <v>39327.2529</v>
+      </c>
+      <c r="Y111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9" t="n">
+        <v>45790.7811</v>
+      </c>
+      <c r="AB111" s="9" t="n">
+        <v>3524.1123</v>
+      </c>
+      <c r="AC111" s="9" t="n">
+        <v>39327.2529</v>
+      </c>
+      <c r="AD111" s="9" t="n">
+        <v>43053.5799</v>
+      </c>
+      <c r="AE111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="9" t="n">
+        <v>61982</v>
+      </c>
+      <c r="AG111" s="9" t="n">
+        <v>179265</v>
+      </c>
+      <c r="AH111" s="9" t="n">
+        <v>180500</v>
+      </c>
+      <c r="AI111" s="9" t="n">
+        <v>180010000</v>
+      </c>
+      <c r="AJ111" s="9" t="n">
+        <v>94480000</v>
+      </c>
+      <c r="AK111" s="9" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="AL111" s="9" t="n">
+        <v>46948190</v>
+      </c>
+      <c r="AM111" s="9" t="n">
+        <v>25900000</v>
+      </c>
+      <c r="AN111" s="9" t="n">
+        <v>61610000</v>
+      </c>
+      <c r="AO111" s="9" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="AP111" s="9" t="n">
+        <v>17857200</v>
+      </c>
+      <c r="AQ111" s="9" t="n">
+        <v>2820</v>
+      </c>
+      <c r="AR111" s="9" t="n">
+        <v>205970</v>
+      </c>
+      <c r="AS111" s="9" t="n">
+        <v>4072</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B112" s="9" t="n">
+        <v>4194339376</v>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>90879375</v>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="9" t="n">
+        <v>4074626250</v>
+      </c>
+      <c r="H112" s="9" t="n">
+        <v>545276250</v>
+      </c>
+      <c r="I112" s="9" t="n">
+        <v>7050000000</v>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="9" t="n">
+        <v>8268965626</v>
+      </c>
+      <c r="M112" s="9" t="n">
+        <v>636155625</v>
+      </c>
+      <c r="N112" s="9" t="n">
+        <v>7050000000</v>
+      </c>
+      <c r="O112" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="P112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="9" t="n">
+        <v>23254.7678</v>
+      </c>
+      <c r="R112" s="9" t="n">
+        <v>503.8657</v>
+      </c>
+      <c r="S112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" s="9" t="n">
+        <v>42791.2222</v>
+      </c>
+      <c r="U112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="9" t="n">
+        <v>22591.0037</v>
+      </c>
+      <c r="W112" s="9" t="n">
+        <v>3023.1941</v>
+      </c>
+      <c r="X112" s="9" t="n">
+        <v>39087.6026</v>
+      </c>
+      <c r="Y112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" s="9" t="n">
+        <v>45845.7715</v>
+      </c>
+      <c r="AB112" s="9" t="n">
+        <v>3527.0598</v>
+      </c>
+      <c r="AC112" s="9" t="n">
+        <v>39087.6026</v>
+      </c>
+      <c r="AD112" s="9" t="n">
+        <v>42791.2222</v>
+      </c>
+      <c r="AE112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" s="9" t="n">
+        <v>63096</v>
+      </c>
+      <c r="AG112" s="9" t="n">
+        <v>180365</v>
+      </c>
+      <c r="AH112" s="9" t="n">
+        <v>181758.75</v>
+      </c>
+      <c r="AI112" s="9" t="n">
+        <v>181746250</v>
+      </c>
+      <c r="AJ112" s="9" t="n">
+        <v>95115000</v>
+      </c>
+      <c r="AK112" s="9" t="n">
+        <v>54280000</v>
+      </c>
+      <c r="AL112" s="9" t="n">
+        <v>47191625.5</v>
+      </c>
+      <c r="AM112" s="9" t="n">
+        <v>25900000</v>
+      </c>
+      <c r="AN112" s="9" t="n">
+        <v>61610000</v>
+      </c>
+      <c r="AO112" s="9" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="AP112" s="9" t="n">
+        <v>17965575</v>
+      </c>
+      <c r="AQ112" s="9" t="n">
+        <v>2820</v>
+      </c>
+      <c r="AR112" s="9" t="n">
+        <v>207855</v>
+      </c>
+      <c r="AS112" s="9" t="n">
+        <v>4114.75</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B113" s="9" t="n">
+        <v>4096927676</v>
+      </c>
+      <c r="C113" s="9" t="n">
+        <v>89140000</v>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="F113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="9" t="n">
+        <v>3957965000</v>
+      </c>
+      <c r="H113" s="9" t="n">
+        <v>534840000</v>
+      </c>
+      <c r="I113" s="9" t="n">
+        <v>7285000000</v>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="9" t="n">
+        <v>8054892676</v>
+      </c>
+      <c r="M113" s="9" t="n">
+        <v>623980000</v>
+      </c>
+      <c r="N113" s="9" t="n">
+        <v>7285000000</v>
+      </c>
+      <c r="O113" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="P113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="9" t="n">
+        <v>23120.3593</v>
+      </c>
+      <c r="R113" s="9" t="n">
+        <v>503.0474</v>
+      </c>
+      <c r="S113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" s="9" t="n">
+        <v>43555.3047</v>
+      </c>
+      <c r="U113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="9" t="n">
+        <v>22336.1456</v>
+      </c>
+      <c r="W113" s="9" t="n">
+        <v>3018.2844</v>
+      </c>
+      <c r="X113" s="9" t="n">
+        <v>41111.7381</v>
+      </c>
+      <c r="Y113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" s="9" t="n">
+        <v>45456.5049</v>
+      </c>
+      <c r="AB113" s="9" t="n">
+        <v>3521.3318</v>
+      </c>
+      <c r="AC113" s="9" t="n">
+        <v>41111.7381</v>
+      </c>
+      <c r="AD113" s="9" t="n">
+        <v>43555.3047</v>
+      </c>
+      <c r="AE113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF113" s="9" t="n">
+        <v>64158</v>
+      </c>
+      <c r="AG113" s="9" t="n">
+        <v>177200</v>
+      </c>
+      <c r="AH113" s="9" t="n">
+        <v>178280</v>
+      </c>
+      <c r="AI113" s="9" t="n">
+        <v>176495000</v>
+      </c>
+      <c r="AJ113" s="9" t="n">
+        <v>92870000</v>
+      </c>
+      <c r="AK113" s="9" t="n">
+        <v>52900000</v>
+      </c>
+      <c r="AL113" s="9" t="n">
+        <v>45991838</v>
+      </c>
+      <c r="AM113" s="9" t="n">
+        <v>25900000</v>
+      </c>
+      <c r="AN113" s="9" t="n">
+        <v>61610000</v>
+      </c>
+      <c r="AO113" s="9" t="n">
+        <v>26500000</v>
+      </c>
+      <c r="AP113" s="9" t="n">
+        <v>17500600</v>
+      </c>
+      <c r="AQ113" s="9" t="n">
+        <v>2914</v>
+      </c>
+      <c r="AR113" s="9" t="n">
+        <v>203350</v>
+      </c>
+      <c r="AS113" s="9" t="n">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B114" s="9" t="n">
+        <v>4266808664</v>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>94000000</v>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="9" t="n">
+        <v>4144797500</v>
+      </c>
+      <c r="H114" s="9" t="n">
+        <v>564000000</v>
+      </c>
+      <c r="I114" s="9" t="n">
+        <v>7110000000</v>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="9" t="n">
+        <v>8411606164</v>
+      </c>
+      <c r="M114" s="9" t="n">
+        <v>658000000</v>
+      </c>
+      <c r="N114" s="9" t="n">
+        <v>7110000000</v>
+      </c>
+      <c r="O114" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="P114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="9" t="n">
+        <v>22732.8685</v>
+      </c>
+      <c r="R114" s="9" t="n">
+        <v>500.8167</v>
+      </c>
+      <c r="S114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="9" t="n">
+        <v>41120.3068</v>
+      </c>
+      <c r="U114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="9" t="n">
+        <v>22082.838</v>
+      </c>
+      <c r="W114" s="9" t="n">
+        <v>3004.9002</v>
+      </c>
+      <c r="X114" s="9" t="n">
+        <v>37880.9771</v>
+      </c>
+      <c r="Y114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" s="9" t="n">
+        <v>44815.7065</v>
+      </c>
+      <c r="AB114" s="9" t="n">
+        <v>3505.7169</v>
+      </c>
+      <c r="AC114" s="9" t="n">
+        <v>37880.9771</v>
+      </c>
+      <c r="AD114" s="9" t="n">
+        <v>41120.3068</v>
+      </c>
+      <c r="AE114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF114" s="9" t="n">
+        <v>64546.5</v>
+      </c>
+      <c r="AG114" s="9" t="n">
+        <v>187693.5</v>
+      </c>
+      <c r="AH114" s="9" t="n">
+        <v>188000</v>
+      </c>
+      <c r="AI114" s="9" t="n">
+        <v>185002500</v>
+      </c>
+      <c r="AJ114" s="9" t="n">
+        <v>95540000</v>
+      </c>
+      <c r="AK114" s="9" t="n">
+        <v>54735000</v>
+      </c>
+      <c r="AL114" s="9" t="n">
+        <v>47587207</v>
+      </c>
+      <c r="AM114" s="9" t="n">
+        <v>25900000</v>
+      </c>
+      <c r="AN114" s="9" t="n">
+        <v>61610000</v>
+      </c>
+      <c r="AO114" s="9" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="AP114" s="9" t="n">
+        <v>18333950</v>
+      </c>
+      <c r="AQ114" s="9" t="n">
+        <v>2844</v>
+      </c>
+      <c r="AR114" s="9" t="n">
+        <v>215195</v>
+      </c>
+      <c r="AS114" s="9" t="n">
+        <v>4046.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B115" s="9" t="n">
+        <v>4351819789</v>
+      </c>
+      <c r="C115" s="9" t="n">
+        <v>96590000</v>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="F115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="9" t="n">
+        <v>4214058750</v>
+      </c>
+      <c r="H115" s="9" t="n">
+        <v>579540000</v>
+      </c>
+      <c r="I115" s="9" t="n">
+        <v>7017500000</v>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="9" t="n">
+        <v>8565878539</v>
+      </c>
+      <c r="M115" s="9" t="n">
+        <v>676130000</v>
+      </c>
+      <c r="N115" s="9" t="n">
+        <v>7017500000</v>
+      </c>
+      <c r="O115" s="9" t="n">
+        <v>7718000000</v>
+      </c>
+      <c r="P115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="9" t="n">
+        <v>22534.3921</v>
+      </c>
+      <c r="R115" s="9" t="n">
+        <v>500.1582</v>
+      </c>
+      <c r="S115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" s="9" t="n">
+        <v>39965.0826</v>
+      </c>
+      <c r="U115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="9" t="n">
+        <v>21821.0774</v>
+      </c>
+      <c r="W115" s="9" t="n">
+        <v>3000.949</v>
+      </c>
+      <c r="X115" s="9" t="n">
+        <v>36337.7775</v>
+      </c>
+      <c r="Y115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="9" t="n">
+        <v>44355.4695</v>
+      </c>
+      <c r="AB115" s="9" t="n">
+        <v>3501.1072</v>
+      </c>
+      <c r="AC115" s="9" t="n">
+        <v>36337.7775</v>
+      </c>
+      <c r="AD115" s="9" t="n">
+        <v>39965.0826</v>
+      </c>
+      <c r="AE115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF115" s="9" t="n">
+        <v>64060</v>
+      </c>
+      <c r="AG115" s="9" t="n">
+        <v>193119</v>
+      </c>
+      <c r="AH115" s="9" t="n">
+        <v>193180</v>
+      </c>
+      <c r="AI115" s="9" t="n">
+        <v>188376250</v>
+      </c>
+      <c r="AJ115" s="9" t="n">
+        <v>95797500</v>
+      </c>
+      <c r="AK115" s="9" t="n">
+        <v>54120000</v>
+      </c>
+      <c r="AL115" s="9" t="n">
+        <v>47052519.5</v>
+      </c>
+      <c r="AM115" s="9" t="n">
+        <v>25900000</v>
+      </c>
+      <c r="AN115" s="9" t="n">
+        <v>61610000</v>
+      </c>
+      <c r="AO115" s="9" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="AP115" s="9" t="n">
+        <v>18852900</v>
+      </c>
+      <c r="AQ115" s="9" t="n">
+        <v>2807</v>
+      </c>
+      <c r="AR115" s="9" t="n">
+        <v>221452.5</v>
+      </c>
+      <c r="AS115" s="9" t="n">
+        <v>4017</v>
       </c>
     </row>
   </sheetData>
@@ -17216,11 +18206,11 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17257,7 +18247,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>62625</v>
+        <v>64018</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -17271,7 +18261,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17282,7 +18272,7 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>174200</v>
+        <v>193400</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
@@ -17296,7 +18286,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17307,7 +18297,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>175100</v>
+        <v>193400</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
@@ -17321,7 +18311,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17332,7 +18322,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>178505000</v>
+        <v>188510000</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
@@ -17346,7 +18336,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17357,7 +18347,7 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>93600000</v>
+        <v>95940000</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -17371,7 +18361,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17382,7 +18372,7 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>54000000</v>
+        <v>54060000</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
@@ -17396,7 +18386,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17407,7 +18397,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>46948190</v>
+        <v>47000355</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -17421,7 +18411,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17446,7 +18436,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17471,7 +18461,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17482,7 +18472,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>27500000</v>
+        <v>28500000</v>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
@@ -17496,7 +18486,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17507,7 +18497,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>17702300</v>
+        <v>18894900</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
@@ -17521,7 +18511,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17532,7 +18522,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>3060</v>
+        <v>2807</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
@@ -17546,7 +18536,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17557,7 +18547,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>200310</v>
+        <v>221780</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
@@ -17571,7 +18561,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17582,7 +18572,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>4175</v>
+        <v>4017</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
@@ -17596,7 +18586,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>2026-07-05T13:27:36.982033</t>
+          <t>2026-07-18T16:48:34.642516</t>
         </is>
       </c>
     </row>
@@ -17617,11 +18607,11 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17668,7 +18658,7 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>4146930880</v>
+        <v>4358299210</v>
       </c>
       <c r="E2" s="10">
         <f>IFERROR(D2/SUMIFS(D:D,A:A,A2,B:B,B2),0)</f>
@@ -17692,7 +18682,7 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>87550000</v>
+        <v>96700000</v>
       </c>
       <c r="E3" s="10">
         <f>IFERROR(D3/SUMIFS(D:D,A:A,A3,B:B,B3),0)</f>
@@ -17788,7 +18778,7 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>4004205000</v>
+        <v>4216830000</v>
       </c>
       <c r="E7" s="10">
         <f>IFERROR(D7/SUMIFS(D:D,A:A,A7,B:B,B7),0)</f>
@@ -17812,7 +18802,7 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>525300000</v>
+        <v>580200000</v>
       </c>
       <c r="E8" s="10">
         <f>IFERROR(D8/SUMIFS(D:D,A:A,A8,B:B,B8),0)</f>
@@ -17836,7 +18826,7 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>7650000000</v>
+        <v>7017500000</v>
       </c>
       <c r="E9" s="10">
         <f>IFERROR(D9/SUMIFS(D:D,A:A,A9,B:B,B9),0)</f>
@@ -17908,7 +18898,7 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>8151135880</v>
+        <v>8575129210</v>
       </c>
       <c r="E12" s="10">
         <f>IFERROR(D12/SUMIFS(D:D,A:A,A12,B:B,B12),0)</f>
@@ -17932,7 +18922,7 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>612850000</v>
+        <v>676900000</v>
       </c>
       <c r="E13" s="10">
         <f>IFERROR(D13/SUMIFS(D:D,A:A,A13,B:B,B13),0)</f>
@@ -17956,7 +18946,7 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>7650000000</v>
+        <v>7017500000</v>
       </c>
       <c r="E14" s="10">
         <f>IFERROR(D14/SUMIFS(D:D,A:A,A14,B:B,B14),0)</f>
@@ -18028,7 +19018,7 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>23805.57336394948</v>
+        <v>22535.15620475698</v>
       </c>
       <c r="E17" s="10">
         <f>IFERROR(D17/SUMIFS(D:D,A:A,A17,B:B,B17),0)</f>
@@ -18052,7 +19042,7 @@
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>502.5832376578645</v>
+        <v>500</v>
       </c>
       <c r="E18" s="10">
         <f>IFERROR(D18/SUMIFS(D:D,A:A,A18,B:B,B18),0)</f>
@@ -18100,7 +19090,7 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>44305.39609644088</v>
+        <v>39906.92864529473</v>
       </c>
       <c r="E20" s="10">
         <f>IFERROR(D20/SUMIFS(D:D,A:A,A20,B:B,B20),0)</f>
@@ -18148,7 +19138,7 @@
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>22986.25143513204</v>
+        <v>21803.67114788004</v>
       </c>
       <c r="E22" s="10">
         <f>IFERROR(D22/SUMIFS(D:D,A:A,A22,B:B,B22),0)</f>
@@ -18172,7 +19162,7 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>3015.499425947187</v>
+        <v>3000</v>
       </c>
       <c r="E23" s="10">
         <f>IFERROR(D23/SUMIFS(D:D,A:A,A23,B:B,B23),0)</f>
@@ -18196,7 +19186,7 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>43915.0401836969</v>
+        <v>36284.90175801448</v>
       </c>
       <c r="E24" s="10">
         <f>IFERROR(D24/SUMIFS(D:D,A:A,A24,B:B,B24),0)</f>
@@ -18268,7 +19258,7 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>46791.82479908152</v>
+        <v>44338.82735263703</v>
       </c>
       <c r="E27" s="10">
         <f>IFERROR(D27/SUMIFS(D:D,A:A,A27,B:B,B27),0)</f>
@@ -18292,7 +19282,7 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>3518.082663605052</v>
+        <v>3500</v>
       </c>
       <c r="E28" s="10">
         <f>IFERROR(D28/SUMIFS(D:D,A:A,A28,B:B,B28),0)</f>
@@ -18316,7 +19306,7 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>43915.0401836969</v>
+        <v>36284.90175801448</v>
       </c>
       <c r="E29" s="10">
         <f>IFERROR(D29/SUMIFS(D:D,A:A,A29,B:B,B29),0)</f>
@@ -18340,7 +19330,7 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>44305.39609644088</v>
+        <v>39906.92864529473</v>
       </c>
       <c r="E30" s="10">
         <f>IFERROR(D30/SUMIFS(D:D,A:A,A30,B:B,B30),0)</f>
@@ -18386,19 +19376,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22944,6 +23934,300 @@
       </c>
       <c r="J108" s="9">
         <f>History_Data!P108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11">
+        <f>History_Data!A109</f>
+        <v/>
+      </c>
+      <c r="B109" s="9">
+        <f>History_Data!L109+History_Data!M109+History_Data!N109+History_Data!O109+History_Data!P109</f>
+        <v/>
+      </c>
+      <c r="C109" s="9">
+        <f>History_Data!AA109+History_Data!AB109+History_Data!AC109+History_Data!AD109+History_Data!AE109</f>
+        <v/>
+      </c>
+      <c r="D109" s="9">
+        <f>History_Data!B109+History_Data!C109+History_Data!D109+History_Data!E109+History_Data!F109</f>
+        <v/>
+      </c>
+      <c r="E109" s="9">
+        <f>History_Data!G109+History_Data!H109+History_Data!I109+History_Data!J109+History_Data!K109</f>
+        <v/>
+      </c>
+      <c r="F109" s="9">
+        <f>History_Data!L109</f>
+        <v/>
+      </c>
+      <c r="G109" s="9">
+        <f>History_Data!M109</f>
+        <v/>
+      </c>
+      <c r="H109" s="9">
+        <f>History_Data!N109</f>
+        <v/>
+      </c>
+      <c r="I109" s="9">
+        <f>History_Data!O109</f>
+        <v/>
+      </c>
+      <c r="J109" s="9">
+        <f>History_Data!P109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11">
+        <f>History_Data!A110</f>
+        <v/>
+      </c>
+      <c r="B110" s="9">
+        <f>History_Data!L110+History_Data!M110+History_Data!N110+History_Data!O110+History_Data!P110</f>
+        <v/>
+      </c>
+      <c r="C110" s="9">
+        <f>History_Data!AA110+History_Data!AB110+History_Data!AC110+History_Data!AD110+History_Data!AE110</f>
+        <v/>
+      </c>
+      <c r="D110" s="9">
+        <f>History_Data!B110+History_Data!C110+History_Data!D110+History_Data!E110+History_Data!F110</f>
+        <v/>
+      </c>
+      <c r="E110" s="9">
+        <f>History_Data!G110+History_Data!H110+History_Data!I110+History_Data!J110+History_Data!K110</f>
+        <v/>
+      </c>
+      <c r="F110" s="9">
+        <f>History_Data!L110</f>
+        <v/>
+      </c>
+      <c r="G110" s="9">
+        <f>History_Data!M110</f>
+        <v/>
+      </c>
+      <c r="H110" s="9">
+        <f>History_Data!N110</f>
+        <v/>
+      </c>
+      <c r="I110" s="9">
+        <f>History_Data!O110</f>
+        <v/>
+      </c>
+      <c r="J110" s="9">
+        <f>History_Data!P110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11">
+        <f>History_Data!A111</f>
+        <v/>
+      </c>
+      <c r="B111" s="9">
+        <f>History_Data!L111+History_Data!M111+History_Data!N111+History_Data!O111+History_Data!P111</f>
+        <v/>
+      </c>
+      <c r="C111" s="9">
+        <f>History_Data!AA111+History_Data!AB111+History_Data!AC111+History_Data!AD111+History_Data!AE111</f>
+        <v/>
+      </c>
+      <c r="D111" s="9">
+        <f>History_Data!B111+History_Data!C111+History_Data!D111+History_Data!E111+History_Data!F111</f>
+        <v/>
+      </c>
+      <c r="E111" s="9">
+        <f>History_Data!G111+History_Data!H111+History_Data!I111+History_Data!J111+History_Data!K111</f>
+        <v/>
+      </c>
+      <c r="F111" s="9">
+        <f>History_Data!L111</f>
+        <v/>
+      </c>
+      <c r="G111" s="9">
+        <f>History_Data!M111</f>
+        <v/>
+      </c>
+      <c r="H111" s="9">
+        <f>History_Data!N111</f>
+        <v/>
+      </c>
+      <c r="I111" s="9">
+        <f>History_Data!O111</f>
+        <v/>
+      </c>
+      <c r="J111" s="9">
+        <f>History_Data!P111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11">
+        <f>History_Data!A112</f>
+        <v/>
+      </c>
+      <c r="B112" s="9">
+        <f>History_Data!L112+History_Data!M112+History_Data!N112+History_Data!O112+History_Data!P112</f>
+        <v/>
+      </c>
+      <c r="C112" s="9">
+        <f>History_Data!AA112+History_Data!AB112+History_Data!AC112+History_Data!AD112+History_Data!AE112</f>
+        <v/>
+      </c>
+      <c r="D112" s="9">
+        <f>History_Data!B112+History_Data!C112+History_Data!D112+History_Data!E112+History_Data!F112</f>
+        <v/>
+      </c>
+      <c r="E112" s="9">
+        <f>History_Data!G112+History_Data!H112+History_Data!I112+History_Data!J112+History_Data!K112</f>
+        <v/>
+      </c>
+      <c r="F112" s="9">
+        <f>History_Data!L112</f>
+        <v/>
+      </c>
+      <c r="G112" s="9">
+        <f>History_Data!M112</f>
+        <v/>
+      </c>
+      <c r="H112" s="9">
+        <f>History_Data!N112</f>
+        <v/>
+      </c>
+      <c r="I112" s="9">
+        <f>History_Data!O112</f>
+        <v/>
+      </c>
+      <c r="J112" s="9">
+        <f>History_Data!P112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11">
+        <f>History_Data!A113</f>
+        <v/>
+      </c>
+      <c r="B113" s="9">
+        <f>History_Data!L113+History_Data!M113+History_Data!N113+History_Data!O113+History_Data!P113</f>
+        <v/>
+      </c>
+      <c r="C113" s="9">
+        <f>History_Data!AA113+History_Data!AB113+History_Data!AC113+History_Data!AD113+History_Data!AE113</f>
+        <v/>
+      </c>
+      <c r="D113" s="9">
+        <f>History_Data!B113+History_Data!C113+History_Data!D113+History_Data!E113+History_Data!F113</f>
+        <v/>
+      </c>
+      <c r="E113" s="9">
+        <f>History_Data!G113+History_Data!H113+History_Data!I113+History_Data!J113+History_Data!K113</f>
+        <v/>
+      </c>
+      <c r="F113" s="9">
+        <f>History_Data!L113</f>
+        <v/>
+      </c>
+      <c r="G113" s="9">
+        <f>History_Data!M113</f>
+        <v/>
+      </c>
+      <c r="H113" s="9">
+        <f>History_Data!N113</f>
+        <v/>
+      </c>
+      <c r="I113" s="9">
+        <f>History_Data!O113</f>
+        <v/>
+      </c>
+      <c r="J113" s="9">
+        <f>History_Data!P113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11">
+        <f>History_Data!A114</f>
+        <v/>
+      </c>
+      <c r="B114" s="9">
+        <f>History_Data!L114+History_Data!M114+History_Data!N114+History_Data!O114+History_Data!P114</f>
+        <v/>
+      </c>
+      <c r="C114" s="9">
+        <f>History_Data!AA114+History_Data!AB114+History_Data!AC114+History_Data!AD114+History_Data!AE114</f>
+        <v/>
+      </c>
+      <c r="D114" s="9">
+        <f>History_Data!B114+History_Data!C114+History_Data!D114+History_Data!E114+History_Data!F114</f>
+        <v/>
+      </c>
+      <c r="E114" s="9">
+        <f>History_Data!G114+History_Data!H114+History_Data!I114+History_Data!J114+History_Data!K114</f>
+        <v/>
+      </c>
+      <c r="F114" s="9">
+        <f>History_Data!L114</f>
+        <v/>
+      </c>
+      <c r="G114" s="9">
+        <f>History_Data!M114</f>
+        <v/>
+      </c>
+      <c r="H114" s="9">
+        <f>History_Data!N114</f>
+        <v/>
+      </c>
+      <c r="I114" s="9">
+        <f>History_Data!O114</f>
+        <v/>
+      </c>
+      <c r="J114" s="9">
+        <f>History_Data!P114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11">
+        <f>History_Data!A115</f>
+        <v/>
+      </c>
+      <c r="B115" s="9">
+        <f>History_Data!L115+History_Data!M115+History_Data!N115+History_Data!O115+History_Data!P115</f>
+        <v/>
+      </c>
+      <c r="C115" s="9">
+        <f>History_Data!AA115+History_Data!AB115+History_Data!AC115+History_Data!AD115+History_Data!AE115</f>
+        <v/>
+      </c>
+      <c r="D115" s="9">
+        <f>History_Data!B115+History_Data!C115+History_Data!D115+History_Data!E115+History_Data!F115</f>
+        <v/>
+      </c>
+      <c r="E115" s="9">
+        <f>History_Data!G115+History_Data!H115+History_Data!I115+History_Data!J115+History_Data!K115</f>
+        <v/>
+      </c>
+      <c r="F115" s="9">
+        <f>History_Data!L115</f>
+        <v/>
+      </c>
+      <c r="G115" s="9">
+        <f>History_Data!M115</f>
+        <v/>
+      </c>
+      <c r="H115" s="9">
+        <f>History_Data!N115</f>
+        <v/>
+      </c>
+      <c r="I115" s="9">
+        <f>History_Data!O115</f>
+        <v/>
+      </c>
+      <c r="J115" s="9">
+        <f>History_Data!P115</f>
         <v/>
       </c>
     </row>
@@ -23052,435 +24336,435 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Bitcoin</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>bitcoin_usd</t>
         </is>
       </c>
-      <c r="C9" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$B$2:$B$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>62625</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$B$2:$B$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>64018</v>
+      </c>
+      <c r="E9" s="19">
         <f>IFERROR($B$4/C9,0)</f>
         <v/>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="19">
         <f>IFERROR(E9*D9,0)</f>
         <v/>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="20">
         <f>IFERROR(F9/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Tether</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>usdt_irt</t>
         </is>
       </c>
-      <c r="C10" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$C$2:$C$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>174200</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="C10" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$C$2:$C$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>193400</v>
+      </c>
+      <c r="E10" s="19">
         <f>IFERROR($B$4/C10,0)</f>
         <v/>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="19">
         <f>IFERROR(E10*D10,0)</f>
         <v/>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="20">
         <f>IFERROR(F10/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>US Dollar</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>usd_cash</t>
         </is>
       </c>
-      <c r="C11" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$D$2:$D$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>175100</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="C11" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$D$2:$D$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>193400</v>
+      </c>
+      <c r="E11" s="19">
         <f>IFERROR($B$4/C11,0)</f>
         <v/>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="19">
         <f>IFERROR(E11*D11,0)</f>
         <v/>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="20">
         <f>IFERROR(F11/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Emami Coin</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>emami_coin</t>
         </is>
       </c>
-      <c r="C12" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$E$2:$E$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>178505000</v>
-      </c>
-      <c r="E12" s="9">
+      <c r="C12" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$E$2:$E$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>188510000</v>
+      </c>
+      <c r="E12" s="19">
         <f>IFERROR($B$4/C12,0)</f>
         <v/>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="19">
         <f>IFERROR(E12*D12,0)</f>
         <v/>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="20">
         <f>IFERROR(F12/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Half Coin</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>half_coin</t>
         </is>
       </c>
-      <c r="C13" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$F$2:$F$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>93600000</v>
-      </c>
-      <c r="E13" s="9">
+      <c r="C13" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$F$2:$F$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>95940000</v>
+      </c>
+      <c r="E13" s="19">
         <f>IFERROR($B$4/C13,0)</f>
         <v/>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="19">
         <f>IFERROR(E13*D13,0)</f>
         <v/>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="20">
         <f>IFERROR(F13/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Quarter Coin</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>quarter_coin</t>
         </is>
       </c>
-      <c r="C14" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$G$2:$G$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>54000000</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="C14" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$G$2:$G$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>54060000</v>
+      </c>
+      <c r="E14" s="19">
         <f>IFERROR($B$4/C14,0)</f>
         <v/>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="19">
         <f>IFERROR(E14*D14,0)</f>
         <v/>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="20">
         <f>IFERROR(F14/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Quarter Coin (Pre-86)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>quarter_coin_pre86</t>
         </is>
       </c>
-      <c r="C15" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$H$2:$H$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>46948190</v>
-      </c>
-      <c r="E15" s="9">
+      <c r="C15" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$H$2:$H$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>47000355</v>
+      </c>
+      <c r="E15" s="19">
         <f>IFERROR($B$4/C15,0)</f>
         <v/>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="19">
         <f>IFERROR(E15*D15,0)</f>
         <v/>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="20">
         <f>IFERROR(F15/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Swiss Gold Bar (1g)</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>swiss_gold_bar_1g</t>
         </is>
       </c>
-      <c r="C16" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$I$2:$I$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="9" t="n">
+      <c r="C16" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$I$2:$I$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="19" t="n">
         <v>25900000</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="19">
         <f>IFERROR($B$4/C16,0)</f>
         <v/>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="19">
         <f>IFERROR(E16*D16,0)</f>
         <v/>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="20">
         <f>IFERROR(F16/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Swiss Gold Bar (2.5g)</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>swiss_gold_bar_2_5g</t>
         </is>
       </c>
-      <c r="C17" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$J$2:$J$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="9" t="n">
+      <c r="C17" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$J$2:$J$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="19" t="n">
         <v>61610000</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="19">
         <f>IFERROR($B$4/C17,0)</f>
         <v/>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="19">
         <f>IFERROR(E17*D17,0)</f>
         <v/>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="20">
         <f>IFERROR(F17/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>1g Coin</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>one_gram_coin</t>
         </is>
       </c>
-      <c r="C18" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$K$2:$K$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="E18" s="9">
+      <c r="C18" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$K$2:$K$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="E18" s="19">
         <f>IFERROR($B$4/C18,0)</f>
         <v/>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="19">
         <f>IFERROR(E18*D18,0)</f>
         <v/>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="20">
         <f>IFERROR(F18/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Gold Gram (18K)</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>gold_18k_gram</t>
         </is>
       </c>
-      <c r="C19" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$L$2:$L$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>17702300</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="C19" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$L$2:$L$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>18894900</v>
+      </c>
+      <c r="E19" s="19">
         <f>IFERROR($B$4/C19,0)</f>
         <v/>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="19">
         <f>IFERROR(E19*D19,0)</f>
         <v/>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="20">
         <f>IFERROR(F19/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>KAMA Stock</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>kama_stock</t>
         </is>
       </c>
-      <c r="C20" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$M$2:$M$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>3060</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="C20" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$M$2:$M$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>2807</v>
+      </c>
+      <c r="E20" s="19">
         <f>IFERROR($B$4/C20,0)</f>
         <v/>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="19">
         <f>IFERROR(E20*D20,0)</f>
         <v/>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="20">
         <f>IFERROR(F20/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Euro</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>euro_cash</t>
         </is>
       </c>
-      <c r="C21" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$N$2:$N$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>200310</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="C21" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$N$2:$N$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>221780</v>
+      </c>
+      <c r="E21" s="19">
         <f>IFERROR($B$4/C21,0)</f>
         <v/>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="19">
         <f>IFERROR(E21*D21,0)</f>
         <v/>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="20">
         <f>IFERROR(F21/$B$4-1,0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Gold Ounce (Global)</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>gold_ounce_usd</t>
         </is>
       </c>
-      <c r="C22" s="9">
-        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$108,History_Data!$O$2:$O$108,"",1),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>4175</v>
-      </c>
-      <c r="E22" s="9">
+      <c r="C22" s="19">
+        <f>IFERROR(XLOOKUP($B$3,History_Data!$A$2:$A$115,History_Data!$O$2:$O$115,"",1),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>4017</v>
+      </c>
+      <c r="E22" s="19">
         <f>IFERROR($B$4/C22,0)</f>
         <v/>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="19">
         <f>IFERROR(E22*D22,0)</f>
         <v/>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="20">
         <f>IFERROR(F22/$B$4-1,0)</f>
         <v/>
       </c>
